--- a/01_기획/02. 컨텐츠/컨텐츠_맵 설정.xlsx
+++ b/01_기획/02. 컨텐츠/컨텐츠_맵 설정.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="14385" yWindow="-15" windowWidth="14430" windowHeight="12060" activeTab="2"/>
+    <workbookView xWindow="14385" yWindow="-15" windowWidth="14430" windowHeight="12060" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="튜토리얼" sheetId="5" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="276">
   <si>
     <t>제목</t>
   </si>
@@ -565,6 +565,323 @@
   </si>
   <si>
     <t>map_s3_001</t>
+  </si>
+  <si>
+    <t>map_s1_005</t>
+  </si>
+  <si>
+    <t>계단이 목표 지점임을 알려 준다.</t>
+  </si>
+  <si>
+    <t>map_s1_006</t>
+  </si>
+  <si>
+    <t>지역 선택을 누르면 튜토리얼을 종료하고 게임을 시작할 수 있음을 알려 준다.</t>
+  </si>
+  <si>
+    <t>map_s1_007</t>
+  </si>
+  <si>
+    <t>하단 메뉴의 기능을 설명한다.</t>
+  </si>
+  <si>
+    <t>map_s1_008</t>
+  </si>
+  <si>
+    <t>map_s1_009</t>
+  </si>
+  <si>
+    <t>설명을 잘 이해했는지 확인한다. 바닥에 아이콘 모양의 타일이 있고 정답 아이콘 위에만 골인필드를 설치한다.</t>
+  </si>
+  <si>
+    <t>map_s1_010</t>
+  </si>
+  <si>
+    <t>시험 2</t>
+  </si>
+  <si>
+    <t>map_s1_011</t>
+  </si>
+  <si>
+    <t>시험 3</t>
+  </si>
+  <si>
+    <t>map_s1_012</t>
+  </si>
+  <si>
+    <t>튜토리얼이 완료 되었음을 알려 주고 선물을 준다.</t>
+  </si>
+  <si>
+    <t>욕심</t>
+  </si>
+  <si>
+    <t>보물에 현혹되지 말고 이동하세요.</t>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>길 양편에 보물상자를 6개 배치, 이 보물상자는 데미지를 주는 보물상자로 열면 캐릭터가 죽는다.</t>
+  </si>
+  <si>
+    <t>죽은 자의 동굴  1층</t>
+  </si>
+  <si>
+    <t>덫을 피해 목표 지점까지 이동하세요.</t>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>바닥에 솟아나는 송곳을 배치함</t>
+  </si>
+  <si>
+    <t>좀비 조심</t>
+  </si>
+  <si>
+    <t>좀비를 피해 목표 지점까지 이동하세요.</t>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>박쥐 사냥</t>
+  </si>
+  <si>
+    <t>박쥐를 모두 처치 하세요.</t>
+  </si>
+  <si>
+    <t>Monster</t>
+  </si>
+  <si>
+    <t>건너편에 박쥐가 오른쪽에서 왼쪽으로 날아 온다. 유저는 원거리 공격으로 박쥐를 공격한다. 한 마리라도 박쥐가 건너편에 도달하면 게임 오버</t>
+  </si>
+  <si>
+    <t>좀비방</t>
+  </si>
+  <si>
+    <t>좀비를 모두 처치 하세요.</t>
+  </si>
+  <si>
+    <t>방에 좀비 두 마리가 있고 모두 처치하면 클리어</t>
+  </si>
+  <si>
+    <t>숨겨진 방으로</t>
+  </si>
+  <si>
+    <t>문을 열고 숨겨진 방으로 이동하세요.</t>
+  </si>
+  <si>
+    <t>길을 문이 막고 있고, 문을 클릭하면 문이 열린다. 문을 여는 방법을 설명한다.</t>
+  </si>
+  <si>
+    <t>보물방</t>
+  </si>
+  <si>
+    <t>믿음</t>
+  </si>
+  <si>
+    <t>목표 지점으로 이동하세요.</t>
+  </si>
+  <si>
+    <t>천사상이 서 있는 곳은 이동할 수 있다. 길이 끈어져 있고 천사상이 아닌 곳으로 가면 떨어져 죽는다.</t>
+  </si>
+  <si>
+    <t>만족</t>
+  </si>
+  <si>
+    <t>제한 시간 안에 목표 지점으로 이동하세요.</t>
+  </si>
+  <si>
+    <t>방에 보물상자가 6개 설치되어 있다. 제한 시간 안에 최대한 많은 보물상자를 열고 다시 목표 지점으로 돌아오면 성공</t>
+  </si>
+  <si>
+    <t>지하 2층으로</t>
+  </si>
+  <si>
+    <t>지하 2층으로 이동하세요</t>
+  </si>
+  <si>
+    <t>Talk</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>죽은 자의 동굴 2층</t>
+  </si>
+  <si>
+    <t>화염을 피해 다음 지역으로 이동하세요</t>
+  </si>
+  <si>
+    <t xml:space="preserve">벽에 화염 발사 오브젝트가 설치되어 있고, 일정 간결으로 화염을 발사한다. </t>
+  </si>
+  <si>
+    <t>구울 조심</t>
+  </si>
+  <si>
+    <t>구울을 피해 다음 지역으로 이동하세요.</t>
+  </si>
+  <si>
+    <t>원거리에서 독을 발사하는 구울을 피해 다음 지역으로 이동한다.</t>
+  </si>
+  <si>
+    <t>함정 1</t>
+  </si>
+  <si>
+    <t>발 밑을 조심하며 다음 지역으로 이동하세요.</t>
+  </si>
+  <si>
+    <t>바닥에 보이지 않는 함정을 설치하여 밟으면 떨어져 죽는다.</t>
+  </si>
+  <si>
+    <t>구울방</t>
+  </si>
+  <si>
+    <t>구울을 모두 처치하세요.</t>
+  </si>
+  <si>
+    <t>구울 2마리 처치</t>
+  </si>
+  <si>
+    <t>함정 2</t>
+  </si>
+  <si>
+    <t>함정과 박쥐 배치</t>
+  </si>
+  <si>
+    <t>라미를 찾아서</t>
+  </si>
+  <si>
+    <t>영혼 수집가 라미를 찾아 보세요.</t>
+  </si>
+  <si>
+    <t>여러 방들 중에 라미가 있는 방을 찾아서 들어가면 클리어, 각 방은 어둠으로 가려져 있다가 유저가 들어가면 밝아진다.</t>
+  </si>
+  <si>
+    <t>라미의 부탁</t>
+  </si>
+  <si>
+    <t>라미와 대화해 보세요.</t>
+  </si>
+  <si>
+    <t>좀비를 처치해 좀비의 영혼을 가져와 달라고 한다.</t>
+  </si>
+  <si>
+    <t>좀비의 영혼</t>
+  </si>
+  <si>
+    <t>좀비를 잡아 좀비의 영혼을 얻으세요.</t>
+  </si>
+  <si>
+    <t>GetItem</t>
+  </si>
+  <si>
+    <t>좀비를 잡아 영혼을 얻자.</t>
+  </si>
+  <si>
+    <t>라미에게 줄 선물</t>
+  </si>
+  <si>
+    <t>라미에게 좀비의 영혼 1개를 주세요.</t>
+  </si>
+  <si>
+    <t>GiveItem</t>
+  </si>
+  <si>
+    <t>좀비 영혼을 가지고 있는 상태에서 라미와 대화하면 영혼이 없어지고 클리어, 영혼이 없는 상태에서는 대사가 나오며 게임 오버</t>
+  </si>
+  <si>
+    <t>라미의 조언</t>
+  </si>
+  <si>
+    <t>라미와 대화해 보세요</t>
+  </si>
+  <si>
+    <t>서큐버스를 찾아서 1</t>
+  </si>
+  <si>
+    <t>서큐버스를 찾으러 이동하세요.</t>
+  </si>
+  <si>
+    <t>서큐버스를 찾아서 2</t>
+  </si>
+  <si>
+    <t>서큐버스 방으로 이동하세요.</t>
+  </si>
+  <si>
+    <t>서큐버스 처치</t>
+  </si>
+  <si>
+    <t>서큐버스를 처치하세요.</t>
+  </si>
+  <si>
+    <t>보스 몬스터인 서큐버스 처치</t>
+  </si>
+  <si>
+    <t>서고로 이동</t>
+  </si>
+  <si>
+    <t>서고로 이동하세요.</t>
+  </si>
+  <si>
+    <t>단서</t>
+  </si>
+  <si>
+    <t>책을 클릭해 샹그리라에 대한 정보를 얻어 보세요.</t>
+  </si>
+  <si>
+    <t>개발자의 방으로</t>
+  </si>
+  <si>
+    <t>개발자와 대화 1</t>
+  </si>
+  <si>
+    <t>개발자와 대화 2</t>
+  </si>
+  <si>
+    <t>개발자와 대화 3</t>
+  </si>
+  <si>
+    <t>개발자와 대화 4</t>
+  </si>
+  <si>
+    <t>개발자의 방으로 이동하세요. 계단을 내려가면 됩니다.</t>
+  </si>
+  <si>
+    <t>개발자와 대화해 보세요. 개발자 근처에 가서 개발자를 터치하세요.</t>
+  </si>
+  <si>
+    <t>개발자에게 메뉴에 대한 설명을 이어서 들어 보세요.</t>
+  </si>
+  <si>
+    <t>개발자와 대화해 보세요.</t>
+  </si>
+  <si>
+    <t>바닥의 아이콘 중 맵선택 아이콘으로 이동하세요.</t>
+  </si>
+  <si>
+    <t>바닥의 아이콘 중 환전 아이콘으로 이동하세요.</t>
+  </si>
+  <si>
+    <t>바닥의 아이콘 중 리뷰 아이콘으로 이동하세요.</t>
+  </si>
+  <si>
+    <t>Talk</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Talk</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>동굴 1층</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화살표로 이동하세요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -638,13 +955,13 @@
       <xdr:col>4</xdr:col>
       <xdr:colOff>152400</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>952500</xdr:rowOff>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>1381125</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>723900</xdr:rowOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>400050</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -667,7 +984,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1524000" y="2619375"/>
+          <a:off x="3171825" y="666750"/>
           <a:ext cx="1228725" cy="1228725"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1990,6 +2307,495 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1352550</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>1333500</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="그림 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2162175" y="295275"/>
+          <a:ext cx="1247775" cy="1247775"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>66675</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1333500</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>1381125</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="그림 2"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2124075" y="1781175"/>
+          <a:ext cx="1266825" cy="1266825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>73800</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>102375</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1381125</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>1409700</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="그림 3"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2131200" y="3226575"/>
+          <a:ext cx="1307325" cy="1307325"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>42825</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>61875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1395525</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>1414575</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="그림 4"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2100225" y="4643400"/>
+          <a:ext cx="1352700" cy="1352700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>49950</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>40425</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1402650</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>1393125</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="그림 5"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2107350" y="6079275"/>
+          <a:ext cx="1352700" cy="1352700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>38025</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>47550</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1390725</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>1400250</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="그림 6"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2095425" y="10458375"/>
+          <a:ext cx="1352700" cy="1352700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>35625</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>35625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1388325</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>1388325</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="그림 7"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2093025" y="8989125"/>
+          <a:ext cx="1352700" cy="1352700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>42750</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>61800</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1395450</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>1414500</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="그림 8"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2100150" y="11929950"/>
+          <a:ext cx="1352700" cy="1352700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>49875</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>49875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1402575</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>1402575</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="그림 9"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2107275" y="13375350"/>
+          <a:ext cx="1352700" cy="1352700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>47475</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>57000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1400175</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>1409700</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="그림 10"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2104875" y="14839800"/>
+          <a:ext cx="1352700" cy="1352700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>38025</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>47550</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1390725</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>1400250</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="그림 11"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2095425" y="7543725"/>
+          <a:ext cx="1352700" cy="1352700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
@@ -2277,7 +3083,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q5"/>
+  <dimension ref="A1:Q13"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="9" customWidth="1"/>
@@ -2338,7 +3144,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2362,7 +3168,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2389,7 +3195,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2416,7 +3222,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2443,10 +3249,242 @@
         <v>124</v>
       </c>
     </row>
+    <row r="6" spans="1:17" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>50045</v>
+      </c>
+      <c r="C6" t="s">
+        <v>173</v>
+      </c>
+      <c r="D6">
+        <v>5003</v>
+      </c>
+      <c r="E6" s="1"/>
+      <c r="F6" t="s">
+        <v>260</v>
+      </c>
+      <c r="G6" t="s">
+        <v>265</v>
+      </c>
+      <c r="H6" t="s">
+        <v>6</v>
+      </c>
+      <c r="I6">
+        <v>99</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>50046</v>
+      </c>
+      <c r="C7" t="s">
+        <v>175</v>
+      </c>
+      <c r="D7">
+        <v>50045</v>
+      </c>
+      <c r="E7" s="1"/>
+      <c r="F7" t="s">
+        <v>261</v>
+      </c>
+      <c r="G7" t="s">
+        <v>266</v>
+      </c>
+      <c r="H7" t="s">
+        <v>272</v>
+      </c>
+      <c r="I7">
+        <v>99</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>50047</v>
+      </c>
+      <c r="C8" t="s">
+        <v>177</v>
+      </c>
+      <c r="D8">
+        <v>50046</v>
+      </c>
+      <c r="E8" s="1"/>
+      <c r="F8" t="s">
+        <v>262</v>
+      </c>
+      <c r="G8" t="s">
+        <v>267</v>
+      </c>
+      <c r="H8" t="s">
+        <v>272</v>
+      </c>
+      <c r="I8">
+        <v>99</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>50048</v>
+      </c>
+      <c r="C9" t="s">
+        <v>179</v>
+      </c>
+      <c r="D9">
+        <v>50047</v>
+      </c>
+      <c r="E9" s="1"/>
+      <c r="F9" t="s">
+        <v>263</v>
+      </c>
+      <c r="G9" t="s">
+        <v>268</v>
+      </c>
+      <c r="H9" t="s">
+        <v>272</v>
+      </c>
+      <c r="I9">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>50049</v>
+      </c>
+      <c r="C10" t="s">
+        <v>180</v>
+      </c>
+      <c r="D10">
+        <v>50048</v>
+      </c>
+      <c r="E10" s="1"/>
+      <c r="F10" t="s">
+        <v>183</v>
+      </c>
+      <c r="G10" t="s">
+        <v>269</v>
+      </c>
+      <c r="H10" t="s">
+        <v>6</v>
+      </c>
+      <c r="I10">
+        <v>99</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>50050</v>
+      </c>
+      <c r="C11" t="s">
+        <v>182</v>
+      </c>
+      <c r="D11">
+        <v>50049</v>
+      </c>
+      <c r="E11" s="1"/>
+      <c r="F11" t="s">
+        <v>185</v>
+      </c>
+      <c r="G11" t="s">
+        <v>270</v>
+      </c>
+      <c r="H11" t="s">
+        <v>6</v>
+      </c>
+      <c r="I11">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>50051</v>
+      </c>
+      <c r="C12" t="s">
+        <v>184</v>
+      </c>
+      <c r="D12">
+        <v>50050</v>
+      </c>
+      <c r="E12" s="1"/>
+      <c r="F12" t="s">
+        <v>185</v>
+      </c>
+      <c r="G12" t="s">
+        <v>271</v>
+      </c>
+      <c r="H12" t="s">
+        <v>6</v>
+      </c>
+      <c r="I12">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>50052</v>
+      </c>
+      <c r="C13" t="s">
+        <v>186</v>
+      </c>
+      <c r="D13">
+        <v>50051</v>
+      </c>
+      <c r="E13" s="1"/>
+      <c r="F13" t="s">
+        <v>264</v>
+      </c>
+      <c r="G13" t="s">
+        <v>268</v>
+      </c>
+      <c r="H13" t="s">
+        <v>273</v>
+      </c>
+      <c r="I13">
+        <v>99</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>187</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="K1:N1"/>
-    <mergeCell ref="E2:E5"/>
+    <mergeCell ref="E2:E6"/>
+    <mergeCell ref="E7:E13"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3718,7 +4756,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:P27"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="3" width="9" customWidth="1"/>
@@ -3776,19 +4814,25 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>50045</v>
+        <v>50053</v>
       </c>
       <c r="C2">
         <v>50038</v>
       </c>
       <c r="E2" t="s">
-        <v>112</v>
+        <v>188</v>
+      </c>
+      <c r="F2" t="s">
+        <v>189</v>
       </c>
       <c r="G2" t="s">
         <v>6</v>
       </c>
       <c r="H2" t="s">
-        <v>125</v>
+        <v>190</v>
+      </c>
+      <c r="P2" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -3796,16 +4840,22 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>50046</v>
+        <v>50054</v>
       </c>
       <c r="E3" t="s">
-        <v>113</v>
+        <v>192</v>
+      </c>
+      <c r="F3" t="s">
+        <v>193</v>
       </c>
       <c r="G3" t="s">
         <v>6</v>
       </c>
       <c r="H3" t="s">
-        <v>125</v>
+        <v>194</v>
+      </c>
+      <c r="P3" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -3813,16 +4863,19 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>50047</v>
+        <v>50055</v>
       </c>
       <c r="E4" t="s">
-        <v>114</v>
+        <v>196</v>
+      </c>
+      <c r="F4" t="s">
+        <v>197</v>
       </c>
       <c r="G4" t="s">
         <v>6</v>
       </c>
       <c r="H4" t="s">
-        <v>125</v>
+        <v>198</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -3830,16 +4883,22 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>50048</v>
+        <v>50056</v>
       </c>
       <c r="E5" t="s">
-        <v>115</v>
+        <v>199</v>
+      </c>
+      <c r="F5" t="s">
+        <v>200</v>
       </c>
       <c r="G5" t="s">
-        <v>6</v>
+        <v>201</v>
       </c>
       <c r="H5" t="s">
-        <v>125</v>
+        <v>190</v>
+      </c>
+      <c r="P5" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -3847,16 +4906,22 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>50049</v>
+        <v>50057</v>
       </c>
       <c r="E6" t="s">
-        <v>116</v>
+        <v>203</v>
+      </c>
+      <c r="F6" t="s">
+        <v>204</v>
       </c>
       <c r="G6" t="s">
-        <v>6</v>
+        <v>201</v>
       </c>
       <c r="H6" t="s">
-        <v>125</v>
+        <v>190</v>
+      </c>
+      <c r="P6" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -3864,16 +4929,22 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>50050</v>
+        <v>50058</v>
       </c>
       <c r="E7" t="s">
-        <v>117</v>
+        <v>206</v>
+      </c>
+      <c r="F7" t="s">
+        <v>207</v>
       </c>
       <c r="G7" t="s">
         <v>6</v>
       </c>
       <c r="H7" t="s">
-        <v>125</v>
+        <v>190</v>
+      </c>
+      <c r="P7" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -3881,16 +4952,19 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>50051</v>
+        <v>50059</v>
       </c>
       <c r="E8" t="s">
-        <v>118</v>
+        <v>209</v>
+      </c>
+      <c r="F8" t="s">
+        <v>77</v>
       </c>
       <c r="G8" t="s">
-        <v>6</v>
+        <v>78</v>
       </c>
       <c r="H8" t="s">
-        <v>125</v>
+        <v>190</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -3898,16 +4972,22 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>50052</v>
+        <v>50060</v>
       </c>
       <c r="E9" t="s">
-        <v>119</v>
+        <v>274</v>
+      </c>
+      <c r="F9" t="s">
+        <v>275</v>
       </c>
       <c r="G9" t="s">
         <v>6</v>
       </c>
       <c r="H9" t="s">
         <v>125</v>
+      </c>
+      <c r="P9" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -3915,16 +4995,22 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>50053</v>
+        <v>50061</v>
       </c>
       <c r="E10" t="s">
-        <v>120</v>
+        <v>210</v>
+      </c>
+      <c r="F10" t="s">
+        <v>211</v>
       </c>
       <c r="G10" t="s">
         <v>6</v>
       </c>
       <c r="H10" t="s">
-        <v>125</v>
+        <v>190</v>
+      </c>
+      <c r="P10" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -3932,16 +5018,372 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>50054</v>
+        <v>50062</v>
       </c>
       <c r="E11" t="s">
-        <v>121</v>
+        <v>213</v>
+      </c>
+      <c r="F11" t="s">
+        <v>214</v>
       </c>
       <c r="G11" t="s">
-        <v>96</v>
+        <v>6</v>
       </c>
       <c r="H11" t="s">
-        <v>125</v>
+        <v>190</v>
+      </c>
+      <c r="P11" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>50063</v>
+      </c>
+      <c r="E12" t="s">
+        <v>216</v>
+      </c>
+      <c r="F12" t="s">
+        <v>217</v>
+      </c>
+      <c r="G12" t="s">
+        <v>218</v>
+      </c>
+      <c r="H12" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>50064</v>
+      </c>
+      <c r="E13" t="s">
+        <v>219</v>
+      </c>
+      <c r="F13" t="s">
+        <v>220</v>
+      </c>
+      <c r="G13" t="s">
+        <v>6</v>
+      </c>
+      <c r="H13" t="s">
+        <v>190</v>
+      </c>
+      <c r="P13" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>50065</v>
+      </c>
+      <c r="E14" t="s">
+        <v>222</v>
+      </c>
+      <c r="F14" t="s">
+        <v>223</v>
+      </c>
+      <c r="G14" t="s">
+        <v>6</v>
+      </c>
+      <c r="H14" t="s">
+        <v>190</v>
+      </c>
+      <c r="P14" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>50066</v>
+      </c>
+      <c r="E15" t="s">
+        <v>225</v>
+      </c>
+      <c r="F15" t="s">
+        <v>226</v>
+      </c>
+      <c r="G15" t="s">
+        <v>6</v>
+      </c>
+      <c r="H15" t="s">
+        <v>190</v>
+      </c>
+      <c r="P15" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>50067</v>
+      </c>
+      <c r="E16" t="s">
+        <v>228</v>
+      </c>
+      <c r="F16" t="s">
+        <v>229</v>
+      </c>
+      <c r="G16" t="s">
+        <v>201</v>
+      </c>
+      <c r="H16" t="s">
+        <v>190</v>
+      </c>
+      <c r="P16" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>50068</v>
+      </c>
+      <c r="E17" t="s">
+        <v>231</v>
+      </c>
+      <c r="F17" t="s">
+        <v>226</v>
+      </c>
+      <c r="G17" t="s">
+        <v>6</v>
+      </c>
+      <c r="H17" t="s">
+        <v>190</v>
+      </c>
+      <c r="P17" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>50069</v>
+      </c>
+      <c r="E18" t="s">
+        <v>233</v>
+      </c>
+      <c r="F18" t="s">
+        <v>234</v>
+      </c>
+      <c r="G18" t="s">
+        <v>6</v>
+      </c>
+      <c r="H18" t="s">
+        <v>190</v>
+      </c>
+      <c r="P18" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>50070</v>
+      </c>
+      <c r="E19" t="s">
+        <v>236</v>
+      </c>
+      <c r="F19" t="s">
+        <v>237</v>
+      </c>
+      <c r="G19" t="s">
+        <v>218</v>
+      </c>
+      <c r="H19" t="s">
+        <v>190</v>
+      </c>
+      <c r="P19" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>50071</v>
+      </c>
+      <c r="E20" t="s">
+        <v>239</v>
+      </c>
+      <c r="F20" t="s">
+        <v>240</v>
+      </c>
+      <c r="G20" t="s">
+        <v>241</v>
+      </c>
+      <c r="H20" t="s">
+        <v>190</v>
+      </c>
+      <c r="P20" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>50072</v>
+      </c>
+      <c r="E21" t="s">
+        <v>243</v>
+      </c>
+      <c r="F21" t="s">
+        <v>244</v>
+      </c>
+      <c r="G21" t="s">
+        <v>245</v>
+      </c>
+      <c r="H21" t="s">
+        <v>190</v>
+      </c>
+      <c r="P21" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <v>50073</v>
+      </c>
+      <c r="E22" t="s">
+        <v>247</v>
+      </c>
+      <c r="F22" t="s">
+        <v>248</v>
+      </c>
+      <c r="G22" t="s">
+        <v>218</v>
+      </c>
+      <c r="H22" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <v>50074</v>
+      </c>
+      <c r="E23" t="s">
+        <v>249</v>
+      </c>
+      <c r="F23" t="s">
+        <v>250</v>
+      </c>
+      <c r="G23" t="s">
+        <v>6</v>
+      </c>
+      <c r="H23" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24">
+        <v>50075</v>
+      </c>
+      <c r="E24" t="s">
+        <v>251</v>
+      </c>
+      <c r="F24" t="s">
+        <v>252</v>
+      </c>
+      <c r="G24" t="s">
+        <v>6</v>
+      </c>
+      <c r="H24" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25">
+        <v>50076</v>
+      </c>
+      <c r="E25" t="s">
+        <v>253</v>
+      </c>
+      <c r="F25" t="s">
+        <v>254</v>
+      </c>
+      <c r="G25" t="s">
+        <v>201</v>
+      </c>
+      <c r="H25" t="s">
+        <v>190</v>
+      </c>
+      <c r="P25" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26">
+        <v>50077</v>
+      </c>
+      <c r="E26" t="s">
+        <v>256</v>
+      </c>
+      <c r="F26" t="s">
+        <v>257</v>
+      </c>
+      <c r="G26" t="s">
+        <v>6</v>
+      </c>
+      <c r="H26" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27">
+        <v>50078</v>
+      </c>
+      <c r="E27" t="s">
+        <v>258</v>
+      </c>
+      <c r="F27" t="s">
+        <v>259</v>
+      </c>
+      <c r="G27" t="s">
+        <v>218</v>
+      </c>
+      <c r="H27" t="s">
+        <v>190</v>
       </c>
     </row>
   </sheetData>
@@ -3950,6 +5392,7 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/01_기획/02. 컨텐츠/컨텐츠_맵 설정.xlsx
+++ b/01_기획/02. 컨텐츠/컨텐츠_맵 설정.xlsx
@@ -888,7 +888,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -904,6 +904,14 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -913,10 +921,21 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -927,12 +946,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4842,6 +4864,9 @@
       <c r="B3">
         <v>50054</v>
       </c>
+      <c r="C3" s="2">
+        <v>50053</v>
+      </c>
       <c r="E3" t="s">
         <v>192</v>
       </c>
@@ -4865,6 +4890,9 @@
       <c r="B4">
         <v>50055</v>
       </c>
+      <c r="C4" s="2">
+        <v>50054</v>
+      </c>
       <c r="E4" t="s">
         <v>196</v>
       </c>
@@ -4885,6 +4913,9 @@
       <c r="B5">
         <v>50056</v>
       </c>
+      <c r="C5" s="2">
+        <v>50055</v>
+      </c>
       <c r="E5" t="s">
         <v>199</v>
       </c>
@@ -4908,6 +4939,9 @@
       <c r="B6">
         <v>50057</v>
       </c>
+      <c r="C6" s="2">
+        <v>50056</v>
+      </c>
       <c r="E6" t="s">
         <v>203</v>
       </c>
@@ -4930,6 +4964,9 @@
       </c>
       <c r="B7">
         <v>50058</v>
+      </c>
+      <c r="C7" s="2">
+        <v>50057</v>
       </c>
       <c r="E7" t="s">
         <v>206</v>
@@ -4954,6 +4991,9 @@
       <c r="B8">
         <v>50059</v>
       </c>
+      <c r="C8" s="2">
+        <v>50058</v>
+      </c>
       <c r="E8" t="s">
         <v>209</v>
       </c>
@@ -4974,6 +5014,9 @@
       <c r="B9">
         <v>50060</v>
       </c>
+      <c r="C9" s="2">
+        <v>50057</v>
+      </c>
       <c r="E9" t="s">
         <v>274</v>
       </c>
@@ -4997,6 +5040,9 @@
       <c r="B10">
         <v>50061</v>
       </c>
+      <c r="C10" s="2">
+        <v>50060</v>
+      </c>
       <c r="E10" t="s">
         <v>210</v>
       </c>
@@ -5020,6 +5066,9 @@
       <c r="B11">
         <v>50062</v>
       </c>
+      <c r="C11" s="2">
+        <v>50061</v>
+      </c>
       <c r="E11" t="s">
         <v>213</v>
       </c>
@@ -5043,6 +5092,9 @@
       <c r="B12">
         <v>50063</v>
       </c>
+      <c r="C12" s="2">
+        <v>50062</v>
+      </c>
       <c r="E12" t="s">
         <v>216</v>
       </c>
@@ -5063,6 +5115,9 @@
       <c r="B13">
         <v>50064</v>
       </c>
+      <c r="C13" s="2">
+        <v>50063</v>
+      </c>
       <c r="E13" t="s">
         <v>219</v>
       </c>
@@ -5086,6 +5141,9 @@
       <c r="B14">
         <v>50065</v>
       </c>
+      <c r="C14" s="2">
+        <v>50064</v>
+      </c>
       <c r="E14" t="s">
         <v>222</v>
       </c>
@@ -5109,6 +5167,9 @@
       <c r="B15">
         <v>50066</v>
       </c>
+      <c r="C15" s="2">
+        <v>50065</v>
+      </c>
       <c r="E15" t="s">
         <v>225</v>
       </c>
@@ -5132,6 +5193,9 @@
       <c r="B16">
         <v>50067</v>
       </c>
+      <c r="C16" s="2">
+        <v>50066</v>
+      </c>
       <c r="E16" t="s">
         <v>228</v>
       </c>
@@ -5155,6 +5219,9 @@
       <c r="B17">
         <v>50068</v>
       </c>
+      <c r="C17" s="2">
+        <v>50067</v>
+      </c>
       <c r="E17" t="s">
         <v>231</v>
       </c>
@@ -5178,6 +5245,9 @@
       <c r="B18">
         <v>50069</v>
       </c>
+      <c r="C18" s="2">
+        <v>50068</v>
+      </c>
       <c r="E18" t="s">
         <v>233</v>
       </c>
@@ -5201,6 +5271,9 @@
       <c r="B19">
         <v>50070</v>
       </c>
+      <c r="C19" s="2">
+        <v>50069</v>
+      </c>
       <c r="E19" t="s">
         <v>236</v>
       </c>
@@ -5224,6 +5297,9 @@
       <c r="B20">
         <v>50071</v>
       </c>
+      <c r="C20" s="2">
+        <v>50070</v>
+      </c>
       <c r="E20" t="s">
         <v>239</v>
       </c>
@@ -5247,6 +5323,9 @@
       <c r="B21">
         <v>50072</v>
       </c>
+      <c r="C21" s="2">
+        <v>50071</v>
+      </c>
       <c r="E21" t="s">
         <v>243</v>
       </c>
@@ -5270,6 +5349,9 @@
       <c r="B22">
         <v>50073</v>
       </c>
+      <c r="C22" s="2">
+        <v>50072</v>
+      </c>
       <c r="E22" t="s">
         <v>247</v>
       </c>
@@ -5290,6 +5372,9 @@
       <c r="B23">
         <v>50074</v>
       </c>
+      <c r="C23" s="2">
+        <v>50073</v>
+      </c>
       <c r="E23" t="s">
         <v>249</v>
       </c>
@@ -5310,6 +5395,9 @@
       <c r="B24">
         <v>50075</v>
       </c>
+      <c r="C24" s="2">
+        <v>50074</v>
+      </c>
       <c r="E24" t="s">
         <v>251</v>
       </c>
@@ -5330,6 +5418,9 @@
       <c r="B25">
         <v>50076</v>
       </c>
+      <c r="C25" s="2">
+        <v>50075</v>
+      </c>
       <c r="E25" t="s">
         <v>253</v>
       </c>
@@ -5353,6 +5444,9 @@
       <c r="B26">
         <v>50077</v>
       </c>
+      <c r="C26" s="2">
+        <v>50076</v>
+      </c>
       <c r="E26" t="s">
         <v>256</v>
       </c>
@@ -5372,6 +5466,9 @@
       </c>
       <c r="B27">
         <v>50078</v>
+      </c>
+      <c r="C27" s="2">
+        <v>50077</v>
       </c>
       <c r="E27" t="s">
         <v>258</v>

--- a/01_기획/02. 컨텐츠/컨텐츠_맵 설정.xlsx
+++ b/01_기획/02. 컨텐츠/컨텐츠_맵 설정.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="278">
   <si>
     <t>제목</t>
   </si>
@@ -712,9 +712,6 @@
     <t>죽은 자의 동굴 2층</t>
   </si>
   <si>
-    <t>화염을 피해 다음 지역으로 이동하세요</t>
-  </si>
-  <si>
     <t xml:space="preserve">벽에 화염 발사 오브젝트가 설치되어 있고, 일정 간결으로 화염을 발사한다. </t>
   </si>
   <si>
@@ -881,6 +878,18 @@
   </si>
   <si>
     <t>화살표로 이동하세요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>비밀 서고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>제단 앞으로 이동하세요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Move</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -950,11 +959,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2815,6 +2824,710 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1343025</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>1352550</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="그림 12"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2133600" y="17783175"/>
+          <a:ext cx="1266825" cy="1266825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>64275</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>73800</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1371600</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>1381125</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="그림 13"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2121675" y="19228575"/>
+          <a:ext cx="1307325" cy="1307325"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>40425</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>49950</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1393125</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>1402650</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="15" name="그림 14"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2097825" y="20662050"/>
+          <a:ext cx="1352700" cy="1352700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1412175</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>1402650</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="16" name="그림 15"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2105025" y="16278225"/>
+          <a:ext cx="1364550" cy="1364550"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>35700</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>54750</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1400250</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>1419300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="17" name="그림 16"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2093100" y="22124175"/>
+          <a:ext cx="1364550" cy="1364550"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>52350</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>42825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1416900</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>1407375</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="18" name="그림 17"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2109750" y="25026900"/>
+          <a:ext cx="1364550" cy="1364550"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>49950</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>49950</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1414500</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>1414500</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="19" name="그림 18"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2107350" y="32320650"/>
+          <a:ext cx="1364550" cy="1364550"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>38025</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>38025</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1402575</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>1402575</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="20" name="그림 19"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2095425" y="33766050"/>
+          <a:ext cx="1364550" cy="1364550"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>26100</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>45150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1390650</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>1409700</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="21" name="그림 20"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2083500" y="36687825"/>
+          <a:ext cx="1364550" cy="1364550"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>45150</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>73725</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1409700</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>1438275</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="22" name="그림 21"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2102550" y="38173725"/>
+          <a:ext cx="1364550" cy="1364550"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>38025</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>66600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1402575</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>1431150</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="23" name="그림 22"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2095425" y="35251950"/>
+          <a:ext cx="1364550" cy="1364550"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>49950</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>49950</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1414500</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>1414500</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="24" name="그림 23"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2107350" y="30863325"/>
+          <a:ext cx="1364550" cy="1364550"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>40425</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>40425</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1404975</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>1404975</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="25" name="그림 24"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2097825" y="26481825"/>
+          <a:ext cx="1364550" cy="1364550"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>52350</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>42825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1416900</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>1407375</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="26" name="그림 25"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2109750" y="27941550"/>
+          <a:ext cx="1364550" cy="1364550"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>42825</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>42825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1407375</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>1407375</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="27" name="그림 26"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2100225" y="29398875"/>
+          <a:ext cx="1364550" cy="1364550"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>42825</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>52350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1407375</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>1416900</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="28" name="그림 27"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2100225" y="23579100"/>
+          <a:ext cx="1364550" cy="1364550"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -3150,12 +3863,12 @@
       <c r="J1" t="s">
         <v>88</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
       <c r="O1" t="s">
         <v>84</v>
       </c>
@@ -3176,7 +3889,7 @@
       <c r="C2" t="s">
         <v>130</v>
       </c>
-      <c r="E2" s="1"/>
+      <c r="E2" s="2"/>
       <c r="F2" t="s">
         <v>4</v>
       </c>
@@ -3203,7 +3916,7 @@
       <c r="D3">
         <v>50000</v>
       </c>
-      <c r="E3" s="1"/>
+      <c r="E3" s="2"/>
       <c r="F3" t="s">
         <v>7</v>
       </c>
@@ -3230,7 +3943,7 @@
       <c r="D4">
         <v>50001</v>
       </c>
-      <c r="E4" s="1"/>
+      <c r="E4" s="2"/>
       <c r="F4" t="s">
         <v>9</v>
       </c>
@@ -3257,7 +3970,7 @@
       <c r="D5">
         <v>50002</v>
       </c>
-      <c r="E5" s="1"/>
+      <c r="E5" s="2"/>
       <c r="F5" t="s">
         <v>11</v>
       </c>
@@ -3284,12 +3997,12 @@
       <c r="D6">
         <v>5003</v>
       </c>
-      <c r="E6" s="1"/>
+      <c r="E6" s="2"/>
       <c r="F6" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="G6" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H6" t="s">
         <v>6</v>
@@ -3314,15 +4027,15 @@
       <c r="D7">
         <v>50045</v>
       </c>
-      <c r="E7" s="1"/>
+      <c r="E7" s="2"/>
       <c r="F7" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G7" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H7" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="I7">
         <v>99</v>
@@ -3344,15 +4057,15 @@
       <c r="D8">
         <v>50046</v>
       </c>
-      <c r="E8" s="1"/>
+      <c r="E8" s="2"/>
       <c r="F8" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G8" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H8" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="I8">
         <v>99</v>
@@ -3374,15 +4087,15 @@
       <c r="D9">
         <v>50047</v>
       </c>
-      <c r="E9" s="1"/>
+      <c r="E9" s="2"/>
       <c r="F9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G9" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="I9">
         <v>99</v>
@@ -3401,12 +4114,12 @@
       <c r="D10">
         <v>50048</v>
       </c>
-      <c r="E10" s="1"/>
+      <c r="E10" s="2"/>
       <c r="F10" t="s">
         <v>183</v>
       </c>
       <c r="G10" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H10" t="s">
         <v>6</v>
@@ -3431,12 +4144,12 @@
       <c r="D11">
         <v>50049</v>
       </c>
-      <c r="E11" s="1"/>
+      <c r="E11" s="2"/>
       <c r="F11" t="s">
         <v>185</v>
       </c>
       <c r="G11" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H11" t="s">
         <v>6</v>
@@ -3458,12 +4171,12 @@
       <c r="D12">
         <v>50050</v>
       </c>
-      <c r="E12" s="1"/>
+      <c r="E12" s="2"/>
       <c r="F12" t="s">
         <v>185</v>
       </c>
       <c r="G12" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H12" t="s">
         <v>6</v>
@@ -3485,15 +4198,15 @@
       <c r="D13">
         <v>50051</v>
       </c>
-      <c r="E13" s="1"/>
+      <c r="E13" s="2"/>
       <c r="F13" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G13" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H13" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I13">
         <v>99</v>
@@ -3562,12 +4275,12 @@
       <c r="J1" t="s">
         <v>88</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
       <c r="O1" t="s">
         <v>84</v>
       </c>
@@ -3727,7 +4440,7 @@
       <c r="D7">
         <v>50012</v>
       </c>
-      <c r="E7" s="1"/>
+      <c r="E7" s="2"/>
       <c r="F7" t="s">
         <v>25</v>
       </c>
@@ -3757,7 +4470,7 @@
       <c r="D8">
         <v>50013</v>
       </c>
-      <c r="E8" s="1"/>
+      <c r="E8" s="2"/>
       <c r="F8" t="s">
         <v>28</v>
       </c>
@@ -3813,7 +4526,7 @@
       <c r="D10">
         <v>50015</v>
       </c>
-      <c r="E10" s="1"/>
+      <c r="E10" s="2"/>
       <c r="F10" t="s">
         <v>34</v>
       </c>
@@ -3846,7 +4559,7 @@
       <c r="D11">
         <v>50015</v>
       </c>
-      <c r="E11" s="1"/>
+      <c r="E11" s="2"/>
       <c r="F11" t="s">
         <v>38</v>
       </c>
@@ -3879,7 +4592,7 @@
       <c r="D12">
         <v>50015</v>
       </c>
-      <c r="E12" s="1"/>
+      <c r="E12" s="2"/>
       <c r="F12" t="s">
         <v>42</v>
       </c>
@@ -3909,7 +4622,7 @@
       <c r="D13">
         <v>50017</v>
       </c>
-      <c r="E13" s="1"/>
+      <c r="E13" s="2"/>
       <c r="F13" t="s">
         <v>38</v>
       </c>
@@ -3942,7 +4655,7 @@
       <c r="D14">
         <v>50019</v>
       </c>
-      <c r="E14" s="1"/>
+      <c r="E14" s="2"/>
       <c r="F14" t="s">
         <v>47</v>
       </c>
@@ -3975,7 +4688,7 @@
       <c r="D15">
         <v>50019</v>
       </c>
-      <c r="E15" s="1"/>
+      <c r="E15" s="2"/>
       <c r="F15" t="s">
         <v>51</v>
       </c>
@@ -4005,7 +4718,7 @@
       <c r="D16">
         <v>50021</v>
       </c>
-      <c r="E16" s="1"/>
+      <c r="E16" s="2"/>
       <c r="F16" t="s">
         <v>51</v>
       </c>
@@ -4035,7 +4748,7 @@
       <c r="D17">
         <v>50020</v>
       </c>
-      <c r="E17" s="1"/>
+      <c r="E17" s="2"/>
       <c r="F17" t="s">
         <v>55</v>
       </c>
@@ -4094,7 +4807,7 @@
       <c r="D19">
         <v>50007</v>
       </c>
-      <c r="E19" s="1"/>
+      <c r="E19" s="2"/>
       <c r="F19" t="s">
         <v>60</v>
       </c>
@@ -4124,7 +4837,7 @@
       <c r="D20">
         <v>50008</v>
       </c>
-      <c r="E20" s="1"/>
+      <c r="E20" s="2"/>
       <c r="F20" t="s">
         <v>64</v>
       </c>
@@ -4177,7 +4890,7 @@
       <c r="D22">
         <v>50010</v>
       </c>
-      <c r="E22" s="1"/>
+      <c r="E22" s="2"/>
       <c r="F22" t="s">
         <v>60</v>
       </c>
@@ -4207,7 +4920,7 @@
       <c r="D23">
         <v>50024</v>
       </c>
-      <c r="E23" s="1"/>
+      <c r="E23" s="2"/>
       <c r="F23" t="s">
         <v>69</v>
       </c>
@@ -4234,7 +4947,7 @@
       <c r="D24">
         <v>50025</v>
       </c>
-      <c r="E24" s="1"/>
+      <c r="E24" s="2"/>
       <c r="F24" t="s">
         <v>71</v>
       </c>
@@ -4264,7 +4977,7 @@
       <c r="D25">
         <v>50026</v>
       </c>
-      <c r="E25" s="1"/>
+      <c r="E25" s="2"/>
       <c r="F25" t="s">
         <v>74</v>
       </c>
@@ -4393,12 +5106,12 @@
       <c r="J1" t="s">
         <v>88</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
       <c r="O1" t="s">
         <v>84</v>
       </c>
@@ -4778,7 +5491,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P27"/>
+  <dimension ref="A1:P28"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="3" width="9" customWidth="1"/>
@@ -4815,12 +5528,12 @@
       <c r="I1" t="s">
         <v>88</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
       <c r="N1" t="s">
         <v>84</v>
       </c>
@@ -4864,7 +5577,7 @@
       <c r="B3">
         <v>50054</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="1">
         <v>50053</v>
       </c>
       <c r="E3" t="s">
@@ -4890,7 +5603,7 @@
       <c r="B4">
         <v>50055</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="1">
         <v>50054</v>
       </c>
       <c r="E4" t="s">
@@ -4913,7 +5626,7 @@
       <c r="B5">
         <v>50056</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="1">
         <v>50055</v>
       </c>
       <c r="E5" t="s">
@@ -4939,7 +5652,7 @@
       <c r="B6">
         <v>50057</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="1">
         <v>50056</v>
       </c>
       <c r="E6" t="s">
@@ -4965,7 +5678,7 @@
       <c r="B7">
         <v>50058</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="1">
         <v>50057</v>
       </c>
       <c r="E7" t="s">
@@ -4991,7 +5704,7 @@
       <c r="B8">
         <v>50059</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="1">
         <v>50058</v>
       </c>
       <c r="E8" t="s">
@@ -5014,14 +5727,14 @@
       <c r="B9">
         <v>50060</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="1">
         <v>50057</v>
       </c>
       <c r="E9" t="s">
+        <v>273</v>
+      </c>
+      <c r="F9" t="s">
         <v>274</v>
-      </c>
-      <c r="F9" t="s">
-        <v>275</v>
       </c>
       <c r="G9" t="s">
         <v>6</v>
@@ -5040,7 +5753,7 @@
       <c r="B10">
         <v>50061</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="1">
         <v>50060</v>
       </c>
       <c r="E10" t="s">
@@ -5066,7 +5779,7 @@
       <c r="B11">
         <v>50062</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11" s="1">
         <v>50061</v>
       </c>
       <c r="E11" t="s">
@@ -5092,7 +5805,7 @@
       <c r="B12">
         <v>50063</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="1">
         <v>50062</v>
       </c>
       <c r="E12" t="s">
@@ -5115,14 +5828,14 @@
       <c r="B13">
         <v>50064</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="1">
         <v>50063</v>
       </c>
       <c r="E13" t="s">
         <v>219</v>
       </c>
       <c r="F13" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="G13" t="s">
         <v>6</v>
@@ -5131,7 +5844,7 @@
         <v>190</v>
       </c>
       <c r="P13" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -5141,14 +5854,14 @@
       <c r="B14">
         <v>50065</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="1">
         <v>50064</v>
       </c>
       <c r="E14" t="s">
+        <v>221</v>
+      </c>
+      <c r="F14" t="s">
         <v>222</v>
-      </c>
-      <c r="F14" t="s">
-        <v>223</v>
       </c>
       <c r="G14" t="s">
         <v>6</v>
@@ -5157,7 +5870,7 @@
         <v>190</v>
       </c>
       <c r="P14" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="15" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -5167,14 +5880,14 @@
       <c r="B15">
         <v>50066</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C15" s="1">
         <v>50065</v>
       </c>
       <c r="E15" t="s">
+        <v>224</v>
+      </c>
+      <c r="F15" t="s">
         <v>225</v>
-      </c>
-      <c r="F15" t="s">
-        <v>226</v>
       </c>
       <c r="G15" t="s">
         <v>6</v>
@@ -5183,7 +5896,7 @@
         <v>190</v>
       </c>
       <c r="P15" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -5193,14 +5906,14 @@
       <c r="B16">
         <v>50067</v>
       </c>
-      <c r="C16" s="2">
+      <c r="C16" s="1">
         <v>50066</v>
       </c>
       <c r="E16" t="s">
+        <v>227</v>
+      </c>
+      <c r="F16" t="s">
         <v>228</v>
-      </c>
-      <c r="F16" t="s">
-        <v>229</v>
       </c>
       <c r="G16" t="s">
         <v>201</v>
@@ -5209,7 +5922,7 @@
         <v>190</v>
       </c>
       <c r="P16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="17" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -5219,14 +5932,14 @@
       <c r="B17">
         <v>50068</v>
       </c>
-      <c r="C17" s="2">
+      <c r="C17" s="1">
         <v>50067</v>
       </c>
       <c r="E17" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F17" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G17" t="s">
         <v>6</v>
@@ -5235,7 +5948,7 @@
         <v>190</v>
       </c>
       <c r="P17" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="18" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -5245,14 +5958,14 @@
       <c r="B18">
         <v>50069</v>
       </c>
-      <c r="C18" s="2">
+      <c r="C18" s="1">
         <v>50068</v>
       </c>
       <c r="E18" t="s">
+        <v>232</v>
+      </c>
+      <c r="F18" t="s">
         <v>233</v>
-      </c>
-      <c r="F18" t="s">
-        <v>234</v>
       </c>
       <c r="G18" t="s">
         <v>6</v>
@@ -5261,7 +5974,7 @@
         <v>190</v>
       </c>
       <c r="P18" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="19" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -5271,14 +5984,14 @@
       <c r="B19">
         <v>50070</v>
       </c>
-      <c r="C19" s="2">
+      <c r="C19" s="1">
         <v>50069</v>
       </c>
       <c r="E19" t="s">
+        <v>235</v>
+      </c>
+      <c r="F19" t="s">
         <v>236</v>
-      </c>
-      <c r="F19" t="s">
-        <v>237</v>
       </c>
       <c r="G19" t="s">
         <v>218</v>
@@ -5287,7 +6000,7 @@
         <v>190</v>
       </c>
       <c r="P19" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="20" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -5297,23 +6010,23 @@
       <c r="B20">
         <v>50071</v>
       </c>
-      <c r="C20" s="2">
+      <c r="C20" s="1">
         <v>50070</v>
       </c>
       <c r="E20" t="s">
+        <v>238</v>
+      </c>
+      <c r="F20" t="s">
         <v>239</v>
       </c>
-      <c r="F20" t="s">
+      <c r="G20" t="s">
         <v>240</v>
-      </c>
-      <c r="G20" t="s">
-        <v>241</v>
       </c>
       <c r="H20" t="s">
         <v>190</v>
       </c>
       <c r="P20" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="21" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -5323,23 +6036,23 @@
       <c r="B21">
         <v>50072</v>
       </c>
-      <c r="C21" s="2">
+      <c r="C21" s="1">
         <v>50071</v>
       </c>
       <c r="E21" t="s">
+        <v>242</v>
+      </c>
+      <c r="F21" t="s">
         <v>243</v>
       </c>
-      <c r="F21" t="s">
+      <c r="G21" t="s">
         <v>244</v>
-      </c>
-      <c r="G21" t="s">
-        <v>245</v>
       </c>
       <c r="H21" t="s">
         <v>190</v>
       </c>
       <c r="P21" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="22" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -5349,14 +6062,14 @@
       <c r="B22">
         <v>50073</v>
       </c>
-      <c r="C22" s="2">
+      <c r="C22" s="1">
         <v>50072</v>
       </c>
       <c r="E22" t="s">
+        <v>246</v>
+      </c>
+      <c r="F22" t="s">
         <v>247</v>
-      </c>
-      <c r="F22" t="s">
-        <v>248</v>
       </c>
       <c r="G22" t="s">
         <v>218</v>
@@ -5372,14 +6085,14 @@
       <c r="B23">
         <v>50074</v>
       </c>
-      <c r="C23" s="2">
+      <c r="C23" s="1">
         <v>50073</v>
       </c>
       <c r="E23" t="s">
+        <v>248</v>
+      </c>
+      <c r="F23" t="s">
         <v>249</v>
-      </c>
-      <c r="F23" t="s">
-        <v>250</v>
       </c>
       <c r="G23" t="s">
         <v>6</v>
@@ -5395,14 +6108,14 @@
       <c r="B24">
         <v>50075</v>
       </c>
-      <c r="C24" s="2">
+      <c r="C24" s="1">
         <v>50074</v>
       </c>
       <c r="E24" t="s">
+        <v>250</v>
+      </c>
+      <c r="F24" t="s">
         <v>251</v>
-      </c>
-      <c r="F24" t="s">
-        <v>252</v>
       </c>
       <c r="G24" t="s">
         <v>6</v>
@@ -5418,14 +6131,14 @@
       <c r="B25">
         <v>50076</v>
       </c>
-      <c r="C25" s="2">
+      <c r="C25" s="1">
         <v>50075</v>
       </c>
       <c r="E25" t="s">
+        <v>252</v>
+      </c>
+      <c r="F25" t="s">
         <v>253</v>
-      </c>
-      <c r="F25" t="s">
-        <v>254</v>
       </c>
       <c r="G25" t="s">
         <v>201</v>
@@ -5434,7 +6147,7 @@
         <v>190</v>
       </c>
       <c r="P25" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="26" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -5444,14 +6157,14 @@
       <c r="B26">
         <v>50077</v>
       </c>
-      <c r="C26" s="2">
+      <c r="C26" s="1">
         <v>50076</v>
       </c>
       <c r="E26" t="s">
+        <v>255</v>
+      </c>
+      <c r="F26" t="s">
         <v>256</v>
-      </c>
-      <c r="F26" t="s">
-        <v>257</v>
       </c>
       <c r="G26" t="s">
         <v>6</v>
@@ -5467,20 +6180,43 @@
       <c r="B27">
         <v>50078</v>
       </c>
-      <c r="C27" s="2">
+      <c r="C27" s="1">
         <v>50077</v>
       </c>
       <c r="E27" t="s">
-        <v>258</v>
+        <v>275</v>
       </c>
       <c r="F27" t="s">
-        <v>259</v>
+        <v>276</v>
       </c>
       <c r="G27" t="s">
-        <v>218</v>
+        <v>277</v>
       </c>
       <c r="H27" t="s">
         <v>190</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" ht="115.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28">
+        <v>50079</v>
+      </c>
+      <c r="C28" s="1">
+        <v>50078</v>
+      </c>
+      <c r="E28" t="s">
+        <v>257</v>
+      </c>
+      <c r="F28" t="s">
+        <v>258</v>
+      </c>
+      <c r="G28" t="s">
+        <v>96</v>
+      </c>
+      <c r="H28" t="s">
+        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -5532,12 +6268,12 @@
       <c r="I1" t="s">
         <v>88</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
       <c r="N1" t="s">
         <v>84</v>
       </c>
@@ -5769,12 +6505,12 @@
       <c r="I1" t="s">
         <v>88</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
       <c r="N1" t="s">
         <v>84</v>
       </c>
@@ -6006,12 +6742,12 @@
       <c r="I1" t="s">
         <v>88</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
       <c r="N1" t="s">
         <v>84</v>
       </c>
@@ -6243,12 +6979,12 @@
       <c r="I1" t="s">
         <v>88</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
       <c r="N1" t="s">
         <v>84</v>
       </c>

--- a/01_기획/02. 컨텐츠/컨텐츠_맵 설정.xlsx
+++ b/01_기획/02. 컨텐츠/컨텐츠_맵 설정.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="14385" yWindow="-15" windowWidth="14430" windowHeight="12060" activeTab="3"/>
+    <workbookView xWindow="14385" yWindow="-15" windowWidth="14430" windowHeight="12060" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="튜토리얼" sheetId="5" r:id="rId1"/>
@@ -12,8 +12,8 @@
     <sheet name="동쪽 숲" sheetId="3" r:id="rId3"/>
     <sheet name="죽은 자의 동굴" sheetId="6" r:id="rId4"/>
     <sheet name="광산 마을" sheetId="8" r:id="rId5"/>
-    <sheet name="버려진 폐광" sheetId="9" r:id="rId6"/>
-    <sheet name="서쪽 숲" sheetId="10" r:id="rId7"/>
+    <sheet name="황무지" sheetId="10" r:id="rId6"/>
+    <sheet name="버려진 폐광" sheetId="9" r:id="rId7"/>
     <sheet name="남쪽 숲" sheetId="11" r:id="rId8"/>
   </sheets>
   <calcPr calcId="145621"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="700" uniqueCount="338">
   <si>
     <t>제목</t>
   </si>
@@ -890,6 +890,247 @@
   </si>
   <si>
     <t>Move</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QuestTalk</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>작클레의 호출</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>마법 연구소로 이동하세요</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>민병대원 마르코와 대화하세요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>작클레와 대화하세요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>리바이의 서가 있을 경우 : 뭔가를 알아내면 알려 주겠다고 한다.
+리바이의 서가 없을 경우 : 바쁘니 귀찮게 하지 말고 가라고 한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>작클레에게 한번 가 보라고 한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>마법 연구소로 이동하세요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>리바이의 서의 비밀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>작클레와 대화하세요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Talk</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자신이 해독하기엔 어려우니 황무지의 누구를 찾아가 보라고 한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>광산마을 여관으로 이동하세요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>광물 조합 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>광물 조합 2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>광물 조합 3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>빈집 털이 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>빈집 털이 2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오른쪽에 있는 집으로 들어가세요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>파머의 고민</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Move</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>상자를 열어서 아이템을 얻고 제한시간 내에 집을 나오세요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>파머와 대화해 보세요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>누군가 자신의 집에서 돈을 훔쳐가서 빈털터리가 되었다고 한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>호박 수확</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>호박 밭으로 가서 호박을 수확하세요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>파머에게 줄 선물</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>광물 조합장 코퍼와 대화하세요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GiveItem</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GetItem</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GetItem</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>묘지로 이동</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>묘지에 귀신이 출몰한다고 하며 처치해 줄 것을 부탁한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>귀신 퇴치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>도둑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조합에서 무언가를 훔쳐 도망가는 도둑을 잡는다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>누군가가 조합에 들어와서 뒤졌다고 한다. 황무지에서 무언가를 발견했는데 그걸 찾는 것 같다고 한다. 황무지로 가 보라고 한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>광산 마을 남쪽으로</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>광산 마을 서쪽으로</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>황무지로</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>보물 창고로</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>보물 창고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reward</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>남쪽 숲으로</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Movie</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>황무지를 클리어 하면 이어진다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>광물 조합장 코퍼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그들이 노리는 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>광물 조합장 코퍼와 대화하세요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>무기 상점으로</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>민병대원 마르코</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>민병대원 산체스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>무기 상인 테츠카</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>마법사 작클레</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>마법 연구소로</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>여관으로</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>여관 주인 줄리아</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전언</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -955,7 +1196,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -964,6 +1205,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3531,6 +3775,1331 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>85726</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>114301</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1359976</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>1388551</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="그림 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2143126" y="323851"/>
+          <a:ext cx="1274250" cy="1274250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>111901</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>111901</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1386151</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>1386151</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="그림 2"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2169301" y="1778776"/>
+          <a:ext cx="1274250" cy="1274250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>99976</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>128551</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1374226</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>1402801</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="그림 3"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2157376" y="3252751"/>
+          <a:ext cx="1274250" cy="1274250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>88051</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>107101</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1362301</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>1381351</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="그림 4"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2145451" y="4688626"/>
+          <a:ext cx="1274250" cy="1274250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>85651</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>76126</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1359901</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>1350376</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="그림 5"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2143051" y="11944276"/>
+          <a:ext cx="1274250" cy="1274250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>92776</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>73726</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1367026</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>1347976</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="그림 6"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2150176" y="13399201"/>
+          <a:ext cx="1274250" cy="1274250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>90376</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>109426</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1364626</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>1383676</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="그림 7"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2147776" y="16349551"/>
+          <a:ext cx="1274250" cy="1274250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>87976</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>87976</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1362226</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>1362226</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="그림 8"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2145376" y="19242751"/>
+          <a:ext cx="1274250" cy="1274250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>85576</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>85576</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1359826</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>1359826</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="그림 9"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2142976" y="22155001"/>
+          <a:ext cx="1274250" cy="1274250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>92701</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>111751</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1366951</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>1386001</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="그림 10"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2150101" y="25095826"/>
+          <a:ext cx="1274250" cy="1274250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>99826</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>80776</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1374076</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>1355026</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="그림 11"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2157226" y="32351476"/>
+          <a:ext cx="1274250" cy="1274250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>97426</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>87901</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1371676</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>1362151</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="그림 12"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2154826" y="30901276"/>
+          <a:ext cx="1274250" cy="1274250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>95026</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>75976</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1369276</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>1350226</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="그림 13"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2152426" y="33804001"/>
+          <a:ext cx="1274250" cy="1274250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>83101</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>92626</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1357351</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>1366876</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="15" name="그림 14"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2140501" y="38192626"/>
+          <a:ext cx="1274250" cy="1274250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>90226</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>99751</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1364476</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>1374001</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="16" name="그림 15"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2147626" y="41114401"/>
+          <a:ext cx="1274250" cy="1274250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>87826</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>87826</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1362076</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>1362076</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="17" name="그림 16"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2145226" y="42559801"/>
+          <a:ext cx="1274250" cy="1274250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>116626</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>126151</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1390876</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>1400401</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="18" name="그림 17"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2174026" y="7622326"/>
+          <a:ext cx="1274250" cy="1274250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>99976</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>99976</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1374226</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>1374226</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="19" name="그림 18"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2157376" y="6138826"/>
+          <a:ext cx="1274250" cy="1274250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>90301</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>80776</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1364551</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>1355026</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="20" name="그림 19"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2147701" y="29436826"/>
+          <a:ext cx="1274250" cy="1274250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>78526</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>116626</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1352776</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>1390876</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="21" name="그림 20"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2135926" y="10527451"/>
+          <a:ext cx="1274250" cy="1274250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>85651</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>76126</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1359901</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>1350376</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="22" name="그림 21"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2143051" y="14858926"/>
+          <a:ext cx="1274250" cy="1274250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>85651</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>85651</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1359901</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>1359901</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="23" name="그림 22"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2143051" y="17783101"/>
+          <a:ext cx="1274250" cy="1274250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>85651</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>85651</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1359901</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>1359901</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="24" name="그림 23"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2143051" y="20697751"/>
+          <a:ext cx="1274250" cy="1274250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>92776</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>64201</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1367026</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>1338451</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="25" name="그림 24"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2150176" y="23590951"/>
+          <a:ext cx="1274250" cy="1274250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>92776</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>73726</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1367026</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>1347976</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="26" name="그림 25"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2150176" y="26515126"/>
+          <a:ext cx="1274250" cy="1274250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>85576</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>95101</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1359826</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>1369351</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="27" name="그림 26"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2142976" y="27993826"/>
+          <a:ext cx="1274250" cy="1274250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>95026</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>85501</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1369276</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>1359751</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="28" name="그림 27"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2152426" y="35270851"/>
+          <a:ext cx="1274250" cy="1274250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>95026</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>104551</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1369276</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>1378801</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="29" name="그림 28"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2152426" y="36747226"/>
+          <a:ext cx="1274250" cy="1274250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>99976</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>119026</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1374226</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>1393276</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="30" name="그림 29"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2157376" y="39676351"/>
+          <a:ext cx="1274250" cy="1274250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>66675</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1371600</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>1381125</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="31" name="그림 30"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2124075" y="9029700"/>
+          <a:ext cx="1304925" cy="1304925"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
@@ -6231,7 +7800,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:P31"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="3" width="9" customWidth="1"/>
@@ -6289,19 +7858,25 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>50045</v>
+        <v>50080</v>
       </c>
       <c r="C2">
-        <v>50038</v>
+        <v>50037</v>
       </c>
       <c r="E2" t="s">
-        <v>112</v>
+        <v>330</v>
+      </c>
+      <c r="F2" t="s">
+        <v>281</v>
       </c>
       <c r="G2" t="s">
-        <v>6</v>
+        <v>96</v>
       </c>
       <c r="H2" t="s">
         <v>125</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -6309,10 +7884,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>50046</v>
+        <v>50081</v>
+      </c>
+      <c r="C3">
+        <v>50080</v>
       </c>
       <c r="E3" t="s">
-        <v>113</v>
+        <v>334</v>
+      </c>
+      <c r="F3" t="s">
+        <v>280</v>
       </c>
       <c r="G3" t="s">
         <v>6</v>
@@ -6326,16 +7907,25 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>50047</v>
+        <v>50082</v>
+      </c>
+      <c r="C4">
+        <v>50081</v>
       </c>
       <c r="E4" t="s">
-        <v>114</v>
+        <v>333</v>
+      </c>
+      <c r="F4" t="s">
+        <v>282</v>
       </c>
       <c r="G4" t="s">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="H4" t="s">
         <v>125</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -6343,10 +7933,16 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>50048</v>
+        <v>50083</v>
+      </c>
+      <c r="C5">
+        <v>50085</v>
       </c>
       <c r="E5" t="s">
-        <v>115</v>
+        <v>279</v>
+      </c>
+      <c r="F5" t="s">
+        <v>285</v>
       </c>
       <c r="G5" t="s">
         <v>6</v>
@@ -6360,16 +7956,25 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>50049</v>
+        <v>50084</v>
+      </c>
+      <c r="C6">
+        <v>50083</v>
       </c>
       <c r="E6" t="s">
-        <v>116</v>
+        <v>286</v>
+      </c>
+      <c r="F6" t="s">
+        <v>287</v>
       </c>
       <c r="G6" t="s">
-        <v>6</v>
+        <v>288</v>
       </c>
       <c r="H6" t="s">
         <v>125</v>
+      </c>
+      <c r="P6" s="3" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -6377,10 +7982,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>50050</v>
+        <v>50085</v>
+      </c>
+      <c r="C7">
+        <v>50080</v>
       </c>
       <c r="E7" t="s">
-        <v>117</v>
+        <v>335</v>
+      </c>
+      <c r="F7" t="s">
+        <v>290</v>
       </c>
       <c r="G7" t="s">
         <v>6</v>
@@ -6394,13 +8005,16 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>50051</v>
+        <v>50086</v>
+      </c>
+      <c r="C8">
+        <v>50085</v>
       </c>
       <c r="E8" t="s">
-        <v>118</v>
+        <v>336</v>
       </c>
       <c r="G8" t="s">
-        <v>6</v>
+        <v>96</v>
       </c>
       <c r="H8" t="s">
         <v>125</v>
@@ -6411,10 +8025,13 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>50052</v>
+        <v>50087</v>
+      </c>
+      <c r="C9">
+        <v>50086</v>
       </c>
       <c r="E9" t="s">
-        <v>119</v>
+        <v>291</v>
       </c>
       <c r="G9" t="s">
         <v>6</v>
@@ -6428,10 +8045,13 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>50053</v>
+        <v>50088</v>
+      </c>
+      <c r="C10">
+        <v>50087</v>
       </c>
       <c r="E10" t="s">
-        <v>120</v>
+        <v>292</v>
       </c>
       <c r="G10" t="s">
         <v>6</v>
@@ -6445,17 +8065,455 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>50054</v>
+        <v>50089</v>
+      </c>
+      <c r="C11">
+        <v>50088</v>
       </c>
       <c r="E11" t="s">
-        <v>121</v>
+        <v>293</v>
       </c>
       <c r="G11" t="s">
-        <v>96</v>
+        <v>298</v>
       </c>
       <c r="H11" t="s">
         <v>125</v>
       </c>
+    </row>
+    <row r="12" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>50090</v>
+      </c>
+      <c r="C12">
+        <v>50088</v>
+      </c>
+      <c r="E12" t="s">
+        <v>294</v>
+      </c>
+      <c r="F12" t="s">
+        <v>296</v>
+      </c>
+      <c r="G12" t="s">
+        <v>277</v>
+      </c>
+      <c r="H12" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>50091</v>
+      </c>
+      <c r="C13">
+        <v>50090</v>
+      </c>
+      <c r="E13" t="s">
+        <v>295</v>
+      </c>
+      <c r="F13" t="s">
+        <v>299</v>
+      </c>
+      <c r="G13" t="s">
+        <v>307</v>
+      </c>
+      <c r="H13" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>50092</v>
+      </c>
+      <c r="C14">
+        <v>50091</v>
+      </c>
+      <c r="E14" t="s">
+        <v>297</v>
+      </c>
+      <c r="F14" t="s">
+        <v>300</v>
+      </c>
+      <c r="G14" t="s">
+        <v>96</v>
+      </c>
+      <c r="H14" t="s">
+        <v>125</v>
+      </c>
+      <c r="P14" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>50093</v>
+      </c>
+      <c r="C15">
+        <v>50092</v>
+      </c>
+      <c r="E15" t="s">
+        <v>302</v>
+      </c>
+      <c r="F15" t="s">
+        <v>303</v>
+      </c>
+      <c r="G15" t="s">
+        <v>308</v>
+      </c>
+      <c r="H15" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>50094</v>
+      </c>
+      <c r="C16">
+        <v>50093</v>
+      </c>
+      <c r="E16" t="s">
+        <v>304</v>
+      </c>
+      <c r="G16" t="s">
+        <v>306</v>
+      </c>
+      <c r="H16" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>50095</v>
+      </c>
+      <c r="C17">
+        <v>50094</v>
+      </c>
+      <c r="E17" t="s">
+        <v>326</v>
+      </c>
+      <c r="F17" t="s">
+        <v>305</v>
+      </c>
+      <c r="G17" t="s">
+        <v>96</v>
+      </c>
+      <c r="H17" t="s">
+        <v>125</v>
+      </c>
+      <c r="P17" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>50096</v>
+      </c>
+      <c r="C18">
+        <v>50095</v>
+      </c>
+      <c r="E18" t="s">
+        <v>309</v>
+      </c>
+      <c r="G18" t="s">
+        <v>277</v>
+      </c>
+      <c r="H18" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>50097</v>
+      </c>
+      <c r="C19">
+        <v>50096</v>
+      </c>
+      <c r="E19" t="s">
+        <v>311</v>
+      </c>
+      <c r="G19" t="s">
+        <v>109</v>
+      </c>
+      <c r="H19" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>50098</v>
+      </c>
+      <c r="C20">
+        <v>50097</v>
+      </c>
+      <c r="E20" t="s">
+        <v>312</v>
+      </c>
+      <c r="G20" t="s">
+        <v>96</v>
+      </c>
+      <c r="H20" t="s">
+        <v>125</v>
+      </c>
+      <c r="P20" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>50099</v>
+      </c>
+      <c r="C21">
+        <v>50098</v>
+      </c>
+      <c r="E21" t="s">
+        <v>327</v>
+      </c>
+      <c r="F21" t="s">
+        <v>328</v>
+      </c>
+      <c r="G21" t="s">
+        <v>96</v>
+      </c>
+      <c r="H21" t="s">
+        <v>125</v>
+      </c>
+      <c r="P21" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <v>50100</v>
+      </c>
+      <c r="C22">
+        <v>50099</v>
+      </c>
+      <c r="E22" t="s">
+        <v>329</v>
+      </c>
+      <c r="G22" t="s">
+        <v>277</v>
+      </c>
+      <c r="H22" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <v>50101</v>
+      </c>
+      <c r="C23">
+        <v>50100</v>
+      </c>
+      <c r="E23" t="s">
+        <v>332</v>
+      </c>
+      <c r="G23" t="s">
+        <v>96</v>
+      </c>
+      <c r="H23" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24">
+        <v>50102</v>
+      </c>
+      <c r="C24">
+        <v>50101</v>
+      </c>
+      <c r="E24" t="s">
+        <v>316</v>
+      </c>
+      <c r="G24" t="s">
+        <v>277</v>
+      </c>
+      <c r="H24" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25">
+        <v>50103</v>
+      </c>
+      <c r="C25">
+        <v>50102</v>
+      </c>
+      <c r="E25" t="s">
+        <v>331</v>
+      </c>
+      <c r="G25" t="s">
+        <v>96</v>
+      </c>
+      <c r="H25" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26">
+        <v>50104</v>
+      </c>
+      <c r="C26">
+        <v>50103</v>
+      </c>
+      <c r="E26" t="s">
+        <v>317</v>
+      </c>
+      <c r="G26" t="s">
+        <v>277</v>
+      </c>
+      <c r="H26" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27">
+        <v>50105</v>
+      </c>
+      <c r="C27">
+        <v>50104</v>
+      </c>
+      <c r="E27" t="s">
+        <v>318</v>
+      </c>
+      <c r="G27" t="s">
+        <v>277</v>
+      </c>
+      <c r="H27" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28">
+        <v>50106</v>
+      </c>
+      <c r="C28">
+        <v>50105</v>
+      </c>
+      <c r="E28" t="s">
+        <v>319</v>
+      </c>
+      <c r="G28" t="s">
+        <v>320</v>
+      </c>
+      <c r="H28" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29">
+        <v>50107</v>
+      </c>
+      <c r="E29" t="s">
+        <v>337</v>
+      </c>
+      <c r="F29" t="s">
+        <v>282</v>
+      </c>
+      <c r="G29" t="s">
+        <v>288</v>
+      </c>
+      <c r="H29" t="s">
+        <v>324</v>
+      </c>
+      <c r="P29" s="3" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30">
+        <v>50108</v>
+      </c>
+      <c r="C30">
+        <v>50107</v>
+      </c>
+      <c r="E30" t="s">
+        <v>315</v>
+      </c>
+      <c r="G30" t="s">
+        <v>322</v>
+      </c>
+      <c r="H30" t="s">
+        <v>323</v>
+      </c>
+      <c r="P30" s="3"/>
+    </row>
+    <row r="31" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31">
+        <v>50109</v>
+      </c>
+      <c r="C31">
+        <v>50108</v>
+      </c>
+      <c r="E31" t="s">
+        <v>321</v>
+      </c>
+      <c r="G31" t="s">
+        <v>322</v>
+      </c>
+      <c r="H31" t="s">
+        <v>323</v>
+      </c>
+      <c r="P31" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -6463,6 +8521,7 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/01_기획/02. 컨텐츠/컨텐츠_맵 설정.xlsx
+++ b/01_기획/02. 컨텐츠/컨텐츠_맵 설정.xlsx
@@ -4,24 +4,25 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="14385" yWindow="-15" windowWidth="14430" windowHeight="12060" activeTab="4"/>
+    <workbookView xWindow="14385" yWindow="-15" windowWidth="14430" windowHeight="12060" tabRatio="687" firstSheet="1" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="튜토리얼" sheetId="5" r:id="rId1"/>
     <sheet name="숲 속 마을" sheetId="2" r:id="rId2"/>
     <sheet name="동쪽 숲" sheetId="3" r:id="rId3"/>
     <sheet name="죽은 자의 동굴" sheetId="6" r:id="rId4"/>
-    <sheet name="광산 마을" sheetId="8" r:id="rId5"/>
+    <sheet name="광산 마을" sheetId="13" r:id="rId5"/>
     <sheet name="황무지" sheetId="10" r:id="rId6"/>
     <sheet name="버려진 폐광" sheetId="9" r:id="rId7"/>
     <sheet name="남쪽 숲" sheetId="11" r:id="rId8"/>
+    <sheet name="메테오라" sheetId="12" r:id="rId9"/>
   </sheets>
   <calcPr calcId="145621"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="700" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="810" uniqueCount="449">
   <si>
     <t>제목</t>
   </si>
@@ -416,10 +417,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>B</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -893,24 +890,62 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>NO</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MapID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>선행 조건</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>등급</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>설명</t>
+  </si>
+  <si>
+    <t>퀘스트 보상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>민병대원 마르코</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Talk</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>오.. 동쪽 숲을 지나 오다니 대단한걸? 묵을 곳은 정했어? 딱히 정한 곳이 없다면 광산마을 여관으로 가봐. 음식은 별로지만 거기 주인인 줄리아는 최고야.</t>
+  </si>
+  <si>
+    <t>작클레에게 한번 가 보라고 한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고고학자</t>
+  </si>
+  <si>
+    <t>고고학자? 글쎄... 고고학자는 모르겠고 작클레씨가 우리 마을에서 제일 똑똑하지. 궁금한게 있으면 마법 연구소에 한번 들려봐</t>
+  </si>
+  <si>
+    <t>마법사 작클레</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>QuestTalk</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>작클레의 호출</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>마법 연구소로 이동하세요</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>민병대원 마르코와 대화하세요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>작클레와 대화하세요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>리바이의 서가 있을 경우 :  난 작클레라고 하네. 네게 뭔가 볼 일이라도? 오.. 이것은!!!! 이걸 해석하려면 꽤 오래 걸리겠군. 뭔가를 알아내면 알려 주겠네. 리바이의 서가 없을 경우 : 난 작클레라고 하네. 네게 뭔가 볼 일이라도? 딱히 일이 없으면 방해하지 말게.</t>
   </si>
   <si>
     <t>리바이의 서가 있을 경우 : 뭔가를 알아내면 알려 주겠다고 한다.
@@ -918,19 +953,94 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>작클레에게 한번 가 보라고 한다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>마법 연구소로 이동하세요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>리바이의 서의 비밀</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>작클레와 대화하세요.</t>
+    <t>리바이의 서의 비밀 1</t>
+  </si>
+  <si>
+    <t>오.. 왔는가? 모두 다 해석한 건 아니지만 이 책은 문을 여는 열쇠인 것 같네. 더 자세한 건 내 능력으론 힘들 것 같군. 아, 최근에 황무지에서 뭔가를 발견했다고 하더군. 일단 광물 조합장 코퍼씨를 만나 보게. </t>
+  </si>
+  <si>
+    <t>자신이 해독하기엔 어려우니 황무지의 누구를 찾아가 보라고 한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>여관으로</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>여관 주인 줄리아</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>어서 오세요. 광산 마을을 처음인가요? 예전만 못하지만 그래도 광산 마을은 풍요로운 곳이랍니다. 뭐 필요한 게 있으면 말씀해 주세요.</t>
+  </si>
+  <si>
+    <t>작클레의 호출</t>
+  </si>
+  <si>
+    <t>여기 계셨군요. 아까 작클레씨가 찾던데 만나 보셨나요? 지금 바로 마법 연구소로 가 보세요.</t>
+  </si>
+  <si>
+    <t>다음 지역으로 이동해 보세요</t>
+  </si>
+  <si>
+    <t>광물 조합으로 들어가세요.</t>
+  </si>
+  <si>
+    <t>Move</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오른쪽에 있는 집으로 들어가세요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>상자를 열어 골드주머니를 획득하세요.</t>
+  </si>
+  <si>
+    <t>GetItem</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>파머의 고민</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QuestTalk</t>
+  </si>
+  <si>
+    <t>골드 주머니가 있는 경우 : 엉엉 ㅠㅠ 누가 우리집에 들어가 내 전 재산을 훔쳐갔어. 뭐, 그게 너라구? 뭐 돈을 돌려 준다니 다행이긴 하지만 도둑질은 나쁜거야. 우리 밭에서 호박을 수확해 준다면 용서해 줄께. 골드가 없는 경우 : 저러다 호박이 다 썩어 버리겠어. 바쁘니까 저리 좀 비켜줄래?</t>
+  </si>
+  <si>
+    <t>누군가 자신의 집에서 돈을 훔쳐가서 빈털터리가 되었다고 한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>호박 수확</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>호박 밭으로 가서 호박을 수확하세요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>호박 밭에서 호박을 클릭해서 얻으면 클리어, 중간 중간에 몹이 섞여 있다. 몹은 움직이지 않고 옆에 가면 공격함</t>
+  </si>
+  <si>
+    <t>파머에게 줄 선물</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>파머에게 수확한 호박 1개를 전해 주세요.</t>
+  </si>
+  <si>
+    <t>GiveItem</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>호박이 있을 경우 : 고마워. 덕분에 걱정을 덜었어. 호박이 없을 경우 : 뭐야? 아직도 안 간거야? 빨리 빨리 하라구.</t>
+  </si>
+  <si>
+    <t>광물 조합장 코퍼</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -938,39 +1048,402 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>자신이 해독하기엔 어려우니 황무지의 누구를 찾아가 보라고 한다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>광산마을 여관으로 이동하세요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>광물 조합 1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>광물 조합 2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>광물 조합 3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>빈집 털이 1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>빈집 털이 2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>오른쪽에 있는 집으로 들어가세요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>파머의 고민</t>
+    <t>묘지에 귀신이 출몰한다고 하며 처치해 줄 것을 부탁한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>리바이의 서의 비밀 2</t>
+  </si>
+  <si>
+    <t>묘지로 이동</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>귀신 퇴치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Monster</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>도둑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조합에서 무언가를 훔쳐 도망가는 도둑을 잡는다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그들이 노리는 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>누군가가 조합에 들어와서 뒤졌다고 한다. 황무지에서 무언가를 발견했는데 그걸 찾는 것 같다고 한다. 황무지로 가 보라고 한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>광산 마을 서쪽으로</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>민병대원 산체스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>황무지로</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>보물 창고로</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>보물 창고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reward</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>황무지를 클리어 하면 이어진다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>광산 마을 남쪽으로</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Movie</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>남쪽 숲으로</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>광물 조합</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>광물 조합으로</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>빈 집으로</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>빈집털이</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>마법 연구소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>마법 연구소로</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>50083,
+50085</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>50088,
+50095</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>50097,
+50099</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>귀신 퇴치 보고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>광물 조합장 코퍼와 대화 하세요.</t>
+  </si>
+  <si>
+    <t>광물 조합장 코퍼와 대화 하세요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NO</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MapID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>선행 조건</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>등급</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>퀘스트 보상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>타이틀</t>
+  </si>
+  <si>
+    <t>비석 앞으로 이동해 비석을 조사해 보세요.</t>
+  </si>
+  <si>
+    <t>비석을 클릭하면 만든 사람들에 대한 설명이 나온다.</t>
+  </si>
+  <si>
+    <t>샹그리아를 찾아서</t>
+  </si>
+  <si>
+    <t>메테오라 안으로 들어가세요.</t>
+  </si>
+  <si>
+    <t>문지기</t>
+  </si>
+  <si>
+    <t>개발자와 대화하세요.</t>
+  </si>
+  <si>
+    <t>용케도 여기까지 왔군요. 현자의 돌 없이 메데이아를 쓰러뜨리다니 대단하군요. 하지만 그 정도로 샹그리아를 찾을 자격이 충분한 것은 아닙니다. 이미 메데이아도 쓰러뜨렸는데 왜 계속 샹그리아를 찾는 건가요?? 당신이 정말 샹그리아를 찾을 자격이 있는지 시험해 볼까요?</t>
+  </si>
+  <si>
+    <t>자격</t>
+  </si>
+  <si>
+    <t>개발자와 대결해 자격을 인정 받으세요.</t>
+  </si>
+  <si>
+    <t>샹그리아로</t>
+  </si>
+  <si>
+    <t>어쩔 수 없군요. 사실 샹그리아는 당신의 가까운 곳에 있습니다. 당신의 사랑하는 가족들이 기다리는 그 곳!! 바로 당신이 가족과 함께하는 그 곳이 샹그리아입니다. 사랑하는 사람과 함께 할 수 있다는 것 보다 더 행복한 곳은 없습니다. 지금 사랑하는 가족과 따뜻한 식사를 함께 해 보세요. 그 동안 수고 많으셨습니다. 이제 가족의 품으로....</t>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>광산 마을 서쪽으로 이동 하세요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>민병대원 산체스와 대화 하세요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>광물 조합장 코퍼와 대화 하세요</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>작클레와 대화 하세요.</t>
+  </si>
+  <si>
+    <t>작클레와 대화 하세요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>민병대원 마르코와 대화 하세요.</t>
+  </si>
+  <si>
+    <t>민병대원 마르코와 대화 하세요</t>
+  </si>
+  <si>
+    <t>줄리아와 대화 하세요.</t>
+  </si>
+  <si>
+    <t>줄리아와 대화 하세요</t>
+  </si>
+  <si>
+    <t>보물 창고로 들어 가세요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>광산 마을 남쪽으로 이동 하세요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>민병대원 카를로스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>민병대원 카를로스와 대화 하세요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>마법 연구소로 이동 하세요</t>
+  </si>
+  <si>
+    <t>광산마을 여관으로 이동 하세요.</t>
+  </si>
+  <si>
+    <t>마법 연구소로 이동 하세요.</t>
+  </si>
+  <si>
+    <t>황무지로 이동 하세요.</t>
+  </si>
+  <si>
+    <t>남쪽 숲으로 이동 하세요.</t>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>탐사 캠프로</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전갈 퇴치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전갈 퇴치 보고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>유적지 조사</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>유적지 조사 보고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>폐광 조사 의뢰</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>폐광 조사</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>폐광 조사 보고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지룡 안타라스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지룡의 둥지로 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지룡의 둥지로 2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지룡 안타라스 퇴치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지룡 퇴치 보고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고대 유적</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>보물 창고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>보물 창고로</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지룡의 둥지로 3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지룡의 둥지로 4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>안타라스의 보물</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>광산 마을로</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>탐사 캠프로 이동 하세요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전갈을 모두 처치 하세요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>유적지의 망령</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>세 곳의 폐광 중 한 곳만 안전한 폐광입니다. 안전한 폐광을 찾으세요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음 지역으로 이동 하세요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지룡의 둥지로 이동 하세요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지룡 안타라스를 처치 하세요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>보물 창고로 이동 하세요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음 지역으로 이동 하세요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지룡의 둥지로 이동 하세요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>보물 상자를 열어 보세요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Monster</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Talk</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Talk</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Talk</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GetItem</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GiveItem</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -978,31 +1451,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>상자를 열어서 아이템을 얻고 제한시간 내에 집을 나오세요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>파머와 대화해 보세요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>누군가 자신의 집에서 돈을 훔쳐가서 빈털터리가 되었다고 한다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>호박 수확</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>호박 밭으로 가서 호박을 수확하세요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>파머에게 줄 선물</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>광물 조합장 코퍼와 대화하세요.</t>
+    <t>Monster</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1010,127 +1459,83 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>Reward</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>GetItem</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>GetItem</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>묘지로 이동</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>묘지에 귀신이 출몰한다고 하며 처치해 줄 것을 부탁한다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>귀신 퇴치</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>도둑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>조합에서 무언가를 훔쳐 도망가는 도둑을 잡는다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>누군가가 조합에 들어와서 뒤졌다고 한다. 황무지에서 무언가를 발견했는데 그걸 찾는 것 같다고 한다. 황무지로 가 보라고 한다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>광산 마을 남쪽으로</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>광산 마을 서쪽으로</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>황무지로</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>보물 창고로</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>보물 창고</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Reward</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>남쪽 숲으로</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Movie</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>A</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>A</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>황무지를 클리어 하면 이어진다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>광물 조합장 코퍼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>그들이 노리는 것</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>광물 조합장 코퍼와 대화하세요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>무기 상점으로</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>민병대원 마르코</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>민병대원 산체스</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>무기 상인 테츠카</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>마법사 작클레</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>마법 연구소로</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>여관으로</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>여관 주인 줄리아</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>전언</t>
+    <t>황무지 탐사대</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>탐사대장 얀센과 대화 하세요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>탐사대장 얀센과 대화 하세요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>탐사대장 얀센과 대화 하세요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>유적지를 조사해 보세요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>탐사대장 얀센에게 점토판 1개를 가져다 주세요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>탐사대장 얀센에게 지룡의 비늘 1개를 가져다 주세요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>귀신을 처치 하세요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>광물 조합에서 나오는 도둑을 잡으세요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>묘지로 이동 하세요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>파머와 대화 하세요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>얀센의 전언</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>레버를 당기면 다리가 생겨서 건너갈 수 있다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>보물상자를 열어 아이템을 얻으면 클리어</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>폐광으로</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>폐광 입구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>폐광으로 들어 가세요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SS</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1204,10 +1609,10 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3780,19 +4185,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>85726</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>114301</xdr:rowOff>
+      <xdr:colOff>126075</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>145124</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1359976</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>1388551</xdr:rowOff>
+      <xdr:colOff>1266977</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>1286026</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="그림 1"/>
+        <xdr:cNvPr id="32" name="그림 31"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -3811,8 +4216,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2143126" y="323851"/>
-          <a:ext cx="1274250" cy="1274250"/>
+          <a:off x="2183475" y="20766749"/>
+          <a:ext cx="1140902" cy="1140902"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3824,19 +4229,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>111901</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>111901</xdr:rowOff>
+      <xdr:colOff>123675</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>114149</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1386151</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>1386151</xdr:rowOff>
+      <xdr:colOff>1264577</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>521626</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="그림 2"/>
+        <xdr:cNvPr id="33" name="그림 32"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -3855,8 +4260,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2169301" y="1778776"/>
-          <a:ext cx="1274250" cy="1274250"/>
+          <a:off x="2181075" y="23650424"/>
+          <a:ext cx="1140902" cy="1140902"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3868,19 +4273,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>99976</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>128551</xdr:rowOff>
+      <xdr:colOff>130800</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>178424</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1374226</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>1402801</xdr:rowOff>
+      <xdr:colOff>1271702</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>1319326</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="그림 3"/>
+        <xdr:cNvPr id="34" name="그림 33"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -3899,8 +4304,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2157376" y="3252751"/>
-          <a:ext cx="1274250" cy="1274250"/>
+          <a:off x="2188200" y="26629349"/>
+          <a:ext cx="1140902" cy="1140902"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3912,19 +4317,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>88051</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>107101</xdr:rowOff>
+      <xdr:colOff>133125</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>142649</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1362301</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>1381351</xdr:rowOff>
+      <xdr:colOff>1274027</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>1283551</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="그림 4"/>
+        <xdr:cNvPr id="37" name="그림 36"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -3943,8 +4348,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2145451" y="4688626"/>
-          <a:ext cx="1274250" cy="1274250"/>
+          <a:off x="2190525" y="35375624"/>
+          <a:ext cx="1140902" cy="1140902"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3956,19 +4361,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>85651</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>76126</xdr:rowOff>
+      <xdr:colOff>121200</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>159299</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1359901</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>1350376</xdr:rowOff>
+      <xdr:colOff>1262102</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>1300201</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="그림 5"/>
+        <xdr:cNvPr id="38" name="그림 37"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -3987,8 +4392,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2143051" y="11944276"/>
-          <a:ext cx="1274250" cy="1274250"/>
+          <a:off x="2178600" y="39764249"/>
+          <a:ext cx="1140902" cy="1140902"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4000,19 +4405,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>92776</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>73726</xdr:rowOff>
+      <xdr:colOff>128325</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>166424</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1367026</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>1347976</xdr:rowOff>
+      <xdr:colOff>1269227</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>1307326</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="그림 6"/>
+        <xdr:cNvPr id="39" name="그림 38"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -4031,8 +4436,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2150176" y="13399201"/>
-          <a:ext cx="1274250" cy="1274250"/>
+          <a:off x="2185725" y="42686024"/>
+          <a:ext cx="1140902" cy="1140902"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4044,19 +4449,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>90376</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>109426</xdr:rowOff>
+      <xdr:colOff>125925</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>154499</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1364626</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>1383676</xdr:rowOff>
+      <xdr:colOff>1266827</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>1295401</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="그림 7"/>
+        <xdr:cNvPr id="40" name="그림 39"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -4075,8 +4480,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2147776" y="16349551"/>
-          <a:ext cx="1274250" cy="1274250"/>
+          <a:off x="2183325" y="44131424"/>
+          <a:ext cx="1140902" cy="1140902"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4088,19 +4493,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>87976</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>87976</xdr:rowOff>
+      <xdr:colOff>123750</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>114224</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1362226</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>1362226</xdr:rowOff>
+      <xdr:colOff>1264652</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>1255126</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="그림 8"/>
+        <xdr:cNvPr id="42" name="그림 41"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -4119,8 +4524,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2145376" y="19242751"/>
-          <a:ext cx="1274250" cy="1274250"/>
+          <a:off x="2181150" y="22193174"/>
+          <a:ext cx="1140902" cy="1140902"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4132,19 +4537,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>85576</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>85576</xdr:rowOff>
+      <xdr:colOff>130875</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>130874</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1359826</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>1359826</xdr:rowOff>
+      <xdr:colOff>1271777</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>1271776</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="그림 9"/>
+        <xdr:cNvPr id="43" name="그림 42"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -4163,8 +4568,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2142976" y="22155001"/>
-          <a:ext cx="1274250" cy="1274250"/>
+          <a:off x="2188275" y="25124474"/>
+          <a:ext cx="1140902" cy="1140902"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4176,39 +4581,39 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>92701</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>111751</xdr:rowOff>
+      <xdr:colOff>130875</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>140399</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1366951</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>1386001</xdr:rowOff>
+      <xdr:colOff>1271777</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>1281301</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="그림 10"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2150101" y="25095826"/>
-          <a:ext cx="1274250" cy="1274250"/>
+        <xdr:cNvPr id="44" name="그림 43"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2188275" y="28048649"/>
+          <a:ext cx="1140902" cy="1140902"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4220,39 +4625,39 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>99826</xdr:colOff>
+      <xdr:colOff>123675</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>171299</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1264577</xdr:colOff>
       <xdr:row>23</xdr:row>
-      <xdr:rowOff>80776</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1374076</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>1355026</xdr:rowOff>
+      <xdr:rowOff>569251</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="그림 11"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2157226" y="32351476"/>
-          <a:ext cx="1274250" cy="1274250"/>
+        <xdr:cNvPr id="45" name="그림 44"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2181075" y="28089074"/>
+          <a:ext cx="1140902" cy="1140902"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4264,39 +4669,39 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>97426</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>87901</xdr:rowOff>
+      <xdr:colOff>133125</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>152174</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1371676</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>1362151</xdr:rowOff>
+      <xdr:colOff>1274027</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>1293076</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="13" name="그림 12"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2154826" y="30901276"/>
-          <a:ext cx="1274250" cy="1274250"/>
+        <xdr:cNvPr id="46" name="그림 45"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2190525" y="36842474"/>
+          <a:ext cx="1140902" cy="1140902"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4308,39 +4713,39 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>95026</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>75976</xdr:rowOff>
+      <xdr:colOff>133125</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>171224</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1369276</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>1350226</xdr:rowOff>
+      <xdr:colOff>1274027</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>1312126</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="14" name="그림 13"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2152426" y="33804001"/>
-          <a:ext cx="1274250" cy="1274250"/>
+        <xdr:cNvPr id="47" name="그림 46"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2190525" y="38318849"/>
+          <a:ext cx="1140902" cy="1140902"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4352,39 +4757,39 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>83101</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>92626</xdr:rowOff>
+      <xdr:colOff>138075</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>185699</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1357351</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>1366876</xdr:rowOff>
+      <xdr:colOff>1278977</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>1326601</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="15" name="그림 14"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2140501" y="38192626"/>
-          <a:ext cx="1274250" cy="1274250"/>
+        <xdr:cNvPr id="48" name="그림 47"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2195475" y="41247974"/>
+          <a:ext cx="1140902" cy="1140902"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4396,39 +4801,39 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>90226</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>99751</xdr:rowOff>
+      <xdr:colOff>123750</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>133274</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1364476</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>1374001</xdr:rowOff>
+      <xdr:colOff>1264652</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>1274176</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="16" name="그림 15"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2147626" y="41114401"/>
-          <a:ext cx="1274250" cy="1274250"/>
+        <xdr:cNvPr id="49" name="그림 48"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2181150" y="12010949"/>
+          <a:ext cx="1140902" cy="1140902"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4440,39 +4845,39 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>87826</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>87826</xdr:rowOff>
+      <xdr:colOff>130875</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1362076</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>1362076</xdr:rowOff>
+      <xdr:colOff>1271777</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>1140902</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="17" name="그림 16"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2145226" y="42559801"/>
-          <a:ext cx="1274250" cy="1274250"/>
+        <xdr:cNvPr id="50" name="그림 49"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2188275" y="14951774"/>
+          <a:ext cx="1140902" cy="1140902"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4484,39 +4889,39 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>116626</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>126151</xdr:rowOff>
+      <xdr:colOff>128475</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>195149</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1390876</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>1400401</xdr:rowOff>
+      <xdr:colOff>1269377</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>1336051</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="18" name="그림 17"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2174026" y="7622326"/>
-          <a:ext cx="1274250" cy="1274250"/>
+        <xdr:cNvPr id="51" name="그림 50"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2185875" y="17902124"/>
+          <a:ext cx="1140902" cy="1140902"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4528,39 +4933,39 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>99976</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>99976</xdr:rowOff>
+      <xdr:colOff>123750</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>161849</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1374226</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>1374226</xdr:rowOff>
+      <xdr:colOff>1264652</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>1302751</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="19" name="그림 18"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2157376" y="6138826"/>
-          <a:ext cx="1274250" cy="1274250"/>
+        <xdr:cNvPr id="53" name="그림 52"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2181150" y="16411499"/>
+          <a:ext cx="1140902" cy="1140902"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4572,39 +4977,39 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>90301</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>80776</xdr:rowOff>
+      <xdr:colOff>123750</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>171374</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1364551</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>1355026</xdr:rowOff>
+      <xdr:colOff>1264652</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>1312276</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="20" name="그림 19"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2147701" y="29436826"/>
-          <a:ext cx="1274250" cy="1274250"/>
+        <xdr:cNvPr id="54" name="그림 53"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2181150" y="19335674"/>
+          <a:ext cx="1140902" cy="1140902"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4616,39 +5021,39 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>78526</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>116626</xdr:rowOff>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>171449</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1352776</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>1390876</xdr:rowOff>
+      <xdr:colOff>1245677</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>578926</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="21" name="그림 20"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2135926" y="10527451"/>
-          <a:ext cx="1274250" cy="1274250"/>
+        <xdr:cNvPr id="55" name="그림 54"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2162175" y="380999"/>
+          <a:ext cx="1140902" cy="1140902"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4660,39 +5065,39 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>85651</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>76126</xdr:rowOff>
+      <xdr:colOff>130950</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>159524</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1359901</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>1350376</xdr:rowOff>
+      <xdr:colOff>1271852</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>1300426</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="22" name="그림 21"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2143051" y="14858926"/>
-          <a:ext cx="1274250" cy="1274250"/>
+        <xdr:cNvPr id="56" name="그림 55"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2188350" y="1835924"/>
+          <a:ext cx="1140902" cy="1140902"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4704,39 +5109,39 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>85651</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>85651</xdr:rowOff>
+      <xdr:colOff>128550</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>176174</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1359901</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>1359901</xdr:rowOff>
+      <xdr:colOff>1269452</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>1317076</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="23" name="그림 22"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2143051" y="17783101"/>
-          <a:ext cx="1274250" cy="1274250"/>
+        <xdr:cNvPr id="57" name="그림 56"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2185950" y="3309899"/>
+          <a:ext cx="1140902" cy="1140902"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4748,39 +5153,39 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>85651</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>85651</xdr:rowOff>
+      <xdr:colOff>145200</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>173774</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1359901</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>1359901</xdr:rowOff>
+      <xdr:colOff>1286102</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>1314676</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="24" name="그림 23"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2143051" y="20697751"/>
-          <a:ext cx="1274250" cy="1274250"/>
+        <xdr:cNvPr id="59" name="그림 58"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2202600" y="7679474"/>
+          <a:ext cx="1140902" cy="1140902"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4792,39 +5197,39 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>92776</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>64201</xdr:rowOff>
+      <xdr:colOff>115905</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>163529</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1367026</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>1338451</xdr:rowOff>
+      <xdr:colOff>1284271</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>1331895</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="25" name="그림 24"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2150176" y="23590951"/>
-          <a:ext cx="1274250" cy="1274250"/>
+        <xdr:cNvPr id="61" name="그림 60"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2173305" y="9126554"/>
+          <a:ext cx="1168366" cy="1168366"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4836,39 +5241,288 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>92776</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>73726</xdr:rowOff>
+      <xdr:colOff>115905</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>134954</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1367026</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>1347976</xdr:rowOff>
+      <xdr:colOff>1284271</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>1303320</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="26" name="그림 25"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2150176" y="26515126"/>
-          <a:ext cx="1274250" cy="1274250"/>
+        <xdr:cNvPr id="64" name="그림 63"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2173305" y="10555304"/>
+          <a:ext cx="1168366" cy="1168366"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>128550</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>147599</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1140902" cy="1140902"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="65" name="그림 64"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2185950" y="6195974"/>
+          <a:ext cx="1140902" cy="1140902"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>130950</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>140474</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1140902" cy="1140902"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="66" name="그림 65"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2188350" y="4731524"/>
+          <a:ext cx="1140902" cy="1140902"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>130875</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>159449</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1140902" cy="1140902"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="67" name="그림 66"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2188275" y="13494449"/>
+          <a:ext cx="1140902" cy="1140902"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>130875</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>130874</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1271777</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>1271776</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="68" name="그림 67"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2188275" y="29534549"/>
+          <a:ext cx="1140902" cy="1140902"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>125925</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>154499</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1140902" cy="1140902"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="69" name="그림 68"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2183325" y="41216774"/>
+          <a:ext cx="1140902" cy="1140902"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>121575</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>112050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1362075</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>1352550</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="그림 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2178975" y="321600"/>
+          <a:ext cx="1240500" cy="1240500"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4880,39 +5534,39 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>85576</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>95101</xdr:rowOff>
+      <xdr:colOff>109650</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>109650</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1359826</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>1369351</xdr:rowOff>
+      <xdr:colOff>1350150</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>1350150</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="27" name="그림 26"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2142976" y="27993826"/>
-          <a:ext cx="1274250" cy="1274250"/>
+        <xdr:cNvPr id="3" name="그림 2"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2167050" y="1776525"/>
+          <a:ext cx="1240500" cy="1240500"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4924,39 +5578,39 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>95026</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>85501</xdr:rowOff>
+      <xdr:colOff>126300</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>116775</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1369276</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>1359751</xdr:rowOff>
+      <xdr:colOff>1366800</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>1357275</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="28" name="그림 27"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2152426" y="35270851"/>
-          <a:ext cx="1274250" cy="1274250"/>
+        <xdr:cNvPr id="4" name="그림 3"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2183700" y="17814225"/>
+          <a:ext cx="1240500" cy="1240500"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4968,39 +5622,39 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>95026</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>104551</xdr:rowOff>
+      <xdr:colOff>104850</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>95325</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1369276</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>1378801</xdr:rowOff>
+      <xdr:colOff>1345350</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>1335825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="29" name="그림 28"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2152426" y="36747226"/>
-          <a:ext cx="1274250" cy="1274250"/>
+        <xdr:cNvPr id="5" name="그림 4"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2162250" y="7591500"/>
+          <a:ext cx="1240500" cy="1240500"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5012,39 +5666,39 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>99976</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>119026</xdr:rowOff>
+      <xdr:colOff>102450</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>83400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1374226</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>1393276</xdr:rowOff>
+      <xdr:colOff>1342950</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>1323900</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="30" name="그림 29"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2157376" y="39676351"/>
-          <a:ext cx="1274250" cy="1274250"/>
+        <xdr:cNvPr id="6" name="그림 5"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2159850" y="23610150"/>
+          <a:ext cx="1240500" cy="1240500"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5056,39 +5710,1051 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>66675</xdr:colOff>
+      <xdr:colOff>100050</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>90525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1340550</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>1331025</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="그림 6"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2157450" y="16330650"/>
+          <a:ext cx="1240500" cy="1240500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>116700</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>107175</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1357200</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>1347675</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="그림 7"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2174100" y="11975325"/>
+          <a:ext cx="1240500" cy="1240500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1354800</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>1373850</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="그림 8"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2171700" y="19288125"/>
+          <a:ext cx="1240500" cy="1240500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>121575</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>102525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1362075</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>1343025</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="그림 9"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2178975" y="3226725"/>
+          <a:ext cx="1240500" cy="1240500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>109650</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>109650</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1350150</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>1350150</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="그림 10"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2167050" y="4691175"/>
+          <a:ext cx="1240500" cy="1240500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>109650</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>100125</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1350150</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>1340625</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="그림 11"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2167050" y="6138975"/>
+          <a:ext cx="1240500" cy="1240500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>109650</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:rowOff>100125</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1371600</xdr:colOff>
+      <xdr:colOff>1350150</xdr:colOff>
       <xdr:row>7</xdr:row>
+      <xdr:rowOff>1340625</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="그림 12"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2167050" y="9053625"/>
+          <a:ext cx="1240500" cy="1240500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>109650</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>81075</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1350150</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>1321575</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="15" name="그림 14"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2167050" y="10491900"/>
+          <a:ext cx="1240500" cy="1240500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>109650</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>90600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1350150</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>1331100</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="16" name="그림 15"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2167050" y="13416075"/>
+          <a:ext cx="1240500" cy="1240500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>109650</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>109650</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1350150</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>1350150</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="17" name="그림 16"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2167050" y="14892450"/>
+          <a:ext cx="1240500" cy="1240500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>109650</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>100125</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1350150</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>1340625</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="18" name="그림 17"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2167050" y="20712225"/>
+          <a:ext cx="1240500" cy="1240500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>109650</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>109650</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1350150</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>1350150</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="19" name="그림 18"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2167050" y="22179075"/>
+          <a:ext cx="1240500" cy="1240500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1352700</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>1352700</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="20" name="그림 19"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2171700" y="25098375"/>
+          <a:ext cx="1238400" cy="1238400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>126300</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>135825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1366800</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>1376325</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="21" name="그림 20"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2183700" y="28034550"/>
+          <a:ext cx="1240500" cy="1240500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>100050</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>109575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1340550</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>1350075</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="22" name="그림 21"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2157450" y="26550975"/>
+          <a:ext cx="1240500" cy="1240500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>109650</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>119175</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1350150</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>1359675</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="24" name="그림 23"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2167050" y="26560575"/>
+          <a:ext cx="1240500" cy="1240500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1240500" cy="1240500"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="25" name="그림 24"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2171700" y="32423100"/>
+          <a:ext cx="1240500" cy="1240500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>126300</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>97725</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1366800</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>1338225</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="26" name="그림 25"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2183700" y="33825750"/>
+          <a:ext cx="1240500" cy="1240500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>109650</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>128700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1350150</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>1369200</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="28" name="그림 27"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2167050" y="32399400"/>
+          <a:ext cx="1240500" cy="1240500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1335900</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>1364475</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="그림 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2114550" y="295275"/>
+          <a:ext cx="1278750" cy="1278750"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>54750</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>83325</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1333500</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>1362075</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="그림 2"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2112150" y="3207525"/>
+          <a:ext cx="1278750" cy="1278750"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1335900</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>1383525</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="그림 3"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2114550" y="1771650"/>
+          <a:ext cx="1278750" cy="1278750"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>54750</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>102375</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1333500</xdr:colOff>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>1381125</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="31" name="그림 30"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2124075" y="9029700"/>
-          <a:ext cx="1304925" cy="1304925"/>
+        <xdr:cNvPr id="5" name="그림 4"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2112150" y="4683900"/>
+          <a:ext cx="1278750" cy="1278750"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>54750</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>73800</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1333500</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>1352550</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="그림 5"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2112150" y="6112650"/>
+          <a:ext cx="1278750" cy="1278750"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5409,7 +7075,7 @@
         <v>83</v>
       </c>
       <c r="C1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D1" t="s">
         <v>97</v>
@@ -5432,12 +7098,12 @@
       <c r="J1" t="s">
         <v>88</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
       <c r="O1" t="s">
         <v>84</v>
       </c>
@@ -5456,9 +7122,9 @@
         <v>50000</v>
       </c>
       <c r="C2" t="s">
-        <v>130</v>
-      </c>
-      <c r="E2" s="2"/>
+        <v>129</v>
+      </c>
+      <c r="E2" s="3"/>
       <c r="F2" t="s">
         <v>4</v>
       </c>
@@ -5468,8 +7134,8 @@
       <c r="H2" t="s">
         <v>6</v>
       </c>
-      <c r="I2" t="s">
-        <v>124</v>
+      <c r="I2">
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:17" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -5480,12 +7146,12 @@
         <v>50001</v>
       </c>
       <c r="C3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D3">
         <v>50000</v>
       </c>
-      <c r="E3" s="2"/>
+      <c r="E3" s="3"/>
       <c r="F3" t="s">
         <v>7</v>
       </c>
@@ -5495,8 +7161,8 @@
       <c r="H3" t="s">
         <v>6</v>
       </c>
-      <c r="I3" t="s">
-        <v>124</v>
+      <c r="I3">
+        <v>99</v>
       </c>
     </row>
     <row r="4" spans="1:17" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -5507,12 +7173,12 @@
         <v>50002</v>
       </c>
       <c r="C4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D4">
         <v>50001</v>
       </c>
-      <c r="E4" s="2"/>
+      <c r="E4" s="3"/>
       <c r="F4" t="s">
         <v>9</v>
       </c>
@@ -5522,8 +7188,8 @@
       <c r="H4" t="s">
         <v>6</v>
       </c>
-      <c r="I4" t="s">
-        <v>124</v>
+      <c r="I4">
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -5534,12 +7200,12 @@
         <v>50003</v>
       </c>
       <c r="C5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D5">
         <v>50002</v>
       </c>
-      <c r="E5" s="2"/>
+      <c r="E5" s="3"/>
       <c r="F5" t="s">
         <v>11</v>
       </c>
@@ -5549,8 +7215,8 @@
       <c r="H5" t="s">
         <v>6</v>
       </c>
-      <c r="I5" t="s">
-        <v>124</v>
+      <c r="I5">
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -5561,17 +7227,17 @@
         <v>50045</v>
       </c>
       <c r="C6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D6">
         <v>5003</v>
       </c>
-      <c r="E6" s="2"/>
+      <c r="E6" s="3"/>
       <c r="F6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H6" t="s">
         <v>6</v>
@@ -5580,7 +7246,7 @@
         <v>99</v>
       </c>
       <c r="Q6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -5591,26 +7257,26 @@
         <v>50046</v>
       </c>
       <c r="C7" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D7">
         <v>50045</v>
       </c>
-      <c r="E7" s="2"/>
+      <c r="E7" s="3"/>
       <c r="F7" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="G7" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I7">
         <v>99</v>
       </c>
       <c r="Q7" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -5621,26 +7287,26 @@
         <v>50047</v>
       </c>
       <c r="C8" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D8">
         <v>50046</v>
       </c>
-      <c r="E8" s="2"/>
+      <c r="E8" s="3"/>
       <c r="F8" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G8" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H8" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I8">
         <v>99</v>
       </c>
       <c r="Q8" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -5651,20 +7317,20 @@
         <v>50048</v>
       </c>
       <c r="C9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D9">
         <v>50047</v>
       </c>
-      <c r="E9" s="2"/>
+      <c r="E9" s="3"/>
       <c r="F9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G9" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H9" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I9">
         <v>99</v>
@@ -5678,17 +7344,17 @@
         <v>50049</v>
       </c>
       <c r="C10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D10">
         <v>50048</v>
       </c>
-      <c r="E10" s="2"/>
+      <c r="E10" s="3"/>
       <c r="F10" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G10" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H10" t="s">
         <v>6</v>
@@ -5697,7 +7363,7 @@
         <v>99</v>
       </c>
       <c r="Q10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11" spans="1:17" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -5708,17 +7374,17 @@
         <v>50050</v>
       </c>
       <c r="C11" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D11">
         <v>50049</v>
       </c>
-      <c r="E11" s="2"/>
+      <c r="E11" s="3"/>
       <c r="F11" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G11" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H11" t="s">
         <v>6</v>
@@ -5735,17 +7401,17 @@
         <v>50051</v>
       </c>
       <c r="C12" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D12">
         <v>50050</v>
       </c>
-      <c r="E12" s="2"/>
+      <c r="E12" s="3"/>
       <c r="F12" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G12" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H12" t="s">
         <v>6</v>
@@ -5762,26 +7428,26 @@
         <v>50052</v>
       </c>
       <c r="C13" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D13">
         <v>50051</v>
       </c>
-      <c r="E13" s="2"/>
+      <c r="E13" s="3"/>
       <c r="F13" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G13" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H13" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="I13">
         <v>99</v>
       </c>
       <c r="Q13" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
   </sheetData>
@@ -5821,7 +7487,7 @@
         <v>83</v>
       </c>
       <c r="C1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D1" t="s">
         <v>98</v>
@@ -5844,12 +7510,12 @@
       <c r="J1" t="s">
         <v>88</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
       <c r="O1" t="s">
         <v>84</v>
       </c>
@@ -5868,7 +7534,7 @@
         <v>50004</v>
       </c>
       <c r="C2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D2">
         <v>50003</v>
@@ -5897,7 +7563,7 @@
         <v>50005</v>
       </c>
       <c r="C3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D3">
         <v>50004</v>
@@ -5923,7 +7589,7 @@
         <v>50006</v>
       </c>
       <c r="C4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D4">
         <v>50005</v>
@@ -5952,7 +7618,7 @@
         <v>50011</v>
       </c>
       <c r="C5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D5">
         <v>50006</v>
@@ -5978,7 +7644,7 @@
         <v>50012</v>
       </c>
       <c r="C6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D6">
         <v>50011</v>
@@ -6004,12 +7670,12 @@
         <v>50013</v>
       </c>
       <c r="C7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D7">
         <v>50012</v>
       </c>
-      <c r="E7" s="2"/>
+      <c r="E7" s="3"/>
       <c r="F7" t="s">
         <v>25</v>
       </c>
@@ -6034,12 +7700,12 @@
         <v>50014</v>
       </c>
       <c r="C8" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D8">
         <v>50013</v>
       </c>
-      <c r="E8" s="2"/>
+      <c r="E8" s="3"/>
       <c r="F8" t="s">
         <v>28</v>
       </c>
@@ -6064,7 +7730,7 @@
         <v>50015</v>
       </c>
       <c r="C9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D9">
         <v>50014</v>
@@ -6090,12 +7756,12 @@
         <v>50016</v>
       </c>
       <c r="C10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D10">
         <v>50015</v>
       </c>
-      <c r="E10" s="2"/>
+      <c r="E10" s="3"/>
       <c r="F10" t="s">
         <v>34</v>
       </c>
@@ -6123,12 +7789,12 @@
         <v>50017</v>
       </c>
       <c r="C11" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D11">
         <v>50015</v>
       </c>
-      <c r="E11" s="2"/>
+      <c r="E11" s="3"/>
       <c r="F11" t="s">
         <v>38</v>
       </c>
@@ -6156,12 +7822,12 @@
         <v>50018</v>
       </c>
       <c r="C12" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D12">
         <v>50015</v>
       </c>
-      <c r="E12" s="2"/>
+      <c r="E12" s="3"/>
       <c r="F12" t="s">
         <v>42</v>
       </c>
@@ -6186,12 +7852,12 @@
         <v>50019</v>
       </c>
       <c r="C13" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D13">
         <v>50017</v>
       </c>
-      <c r="E13" s="2"/>
+      <c r="E13" s="3"/>
       <c r="F13" t="s">
         <v>38</v>
       </c>
@@ -6219,12 +7885,12 @@
         <v>50020</v>
       </c>
       <c r="C14" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D14">
         <v>50019</v>
       </c>
-      <c r="E14" s="2"/>
+      <c r="E14" s="3"/>
       <c r="F14" t="s">
         <v>47</v>
       </c>
@@ -6252,12 +7918,12 @@
         <v>50021</v>
       </c>
       <c r="C15" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D15">
         <v>50019</v>
       </c>
-      <c r="E15" s="2"/>
+      <c r="E15" s="3"/>
       <c r="F15" t="s">
         <v>51</v>
       </c>
@@ -6282,12 +7948,12 @@
         <v>50022</v>
       </c>
       <c r="C16" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D16">
         <v>50021</v>
       </c>
-      <c r="E16" s="2"/>
+      <c r="E16" s="3"/>
       <c r="F16" t="s">
         <v>51</v>
       </c>
@@ -6312,12 +7978,12 @@
         <v>50023</v>
       </c>
       <c r="C17" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D17">
         <v>50020</v>
       </c>
-      <c r="E17" s="2"/>
+      <c r="E17" s="3"/>
       <c r="F17" t="s">
         <v>55</v>
       </c>
@@ -6345,7 +8011,7 @@
         <v>50007</v>
       </c>
       <c r="C18" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D18">
         <v>50023</v>
@@ -6371,12 +8037,12 @@
         <v>50008</v>
       </c>
       <c r="C19" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D19">
         <v>50007</v>
       </c>
-      <c r="E19" s="2"/>
+      <c r="E19" s="3"/>
       <c r="F19" t="s">
         <v>60</v>
       </c>
@@ -6401,12 +8067,12 @@
         <v>50009</v>
       </c>
       <c r="C20" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D20">
         <v>50008</v>
       </c>
-      <c r="E20" s="2"/>
+      <c r="E20" s="3"/>
       <c r="F20" t="s">
         <v>64</v>
       </c>
@@ -6428,7 +8094,7 @@
         <v>50010</v>
       </c>
       <c r="C21" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D21">
         <v>50009</v>
@@ -6454,12 +8120,12 @@
         <v>50024</v>
       </c>
       <c r="C22" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D22">
         <v>50010</v>
       </c>
-      <c r="E22" s="2"/>
+      <c r="E22" s="3"/>
       <c r="F22" t="s">
         <v>60</v>
       </c>
@@ -6484,12 +8150,12 @@
         <v>50025</v>
       </c>
       <c r="C23" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D23">
         <v>50024</v>
       </c>
-      <c r="E23" s="2"/>
+      <c r="E23" s="3"/>
       <c r="F23" t="s">
         <v>69</v>
       </c>
@@ -6511,12 +8177,12 @@
         <v>50026</v>
       </c>
       <c r="C24" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D24">
         <v>50025</v>
       </c>
-      <c r="E24" s="2"/>
+      <c r="E24" s="3"/>
       <c r="F24" t="s">
         <v>71</v>
       </c>
@@ -6541,12 +8207,12 @@
         <v>50027</v>
       </c>
       <c r="C25" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D25">
         <v>50026</v>
       </c>
-      <c r="E25" s="2"/>
+      <c r="E25" s="3"/>
       <c r="F25" t="s">
         <v>74</v>
       </c>
@@ -6568,7 +8234,7 @@
         <v>50028</v>
       </c>
       <c r="C26" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D26">
         <v>50027</v>
@@ -6597,7 +8263,7 @@
         <v>50029</v>
       </c>
       <c r="C27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D27">
         <v>50026</v>
@@ -6655,7 +8321,7 @@
         <v>83</v>
       </c>
       <c r="C1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D1" t="s">
         <v>105</v>
@@ -6675,12 +8341,12 @@
       <c r="J1" t="s">
         <v>88</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
       <c r="O1" t="s">
         <v>84</v>
       </c>
@@ -6699,7 +8365,7 @@
         <v>50030</v>
       </c>
       <c r="C2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D2">
         <v>50029</v>
@@ -6722,7 +8388,7 @@
         <v>50031</v>
       </c>
       <c r="C3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D3">
         <v>50030</v>
@@ -6745,7 +8411,7 @@
         <v>50032</v>
       </c>
       <c r="C4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D4">
         <v>50031</v>
@@ -6768,7 +8434,7 @@
         <v>50033</v>
       </c>
       <c r="C5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D5">
         <v>50032</v>
@@ -6791,7 +8457,7 @@
         <v>50034</v>
       </c>
       <c r="C6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D6">
         <v>50033</v>
@@ -6814,7 +8480,7 @@
         <v>50035</v>
       </c>
       <c r="C7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D7">
         <v>50034</v>
@@ -6837,7 +8503,7 @@
         <v>50036</v>
       </c>
       <c r="C8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D8">
         <v>50035</v>
@@ -6860,7 +8526,7 @@
         <v>50037</v>
       </c>
       <c r="C9" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D9">
         <v>50036</v>
@@ -6883,7 +8549,7 @@
         <v>50038</v>
       </c>
       <c r="C10" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D10">
         <v>50041</v>
@@ -6906,7 +8572,7 @@
         <v>50039</v>
       </c>
       <c r="C11" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D11">
         <v>50044</v>
@@ -6929,7 +8595,7 @@
         <v>50040</v>
       </c>
       <c r="C12" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D12">
         <v>50045</v>
@@ -6952,7 +8618,7 @@
         <v>50041</v>
       </c>
       <c r="C13" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D13">
         <v>50034</v>
@@ -6978,7 +8644,7 @@
         <v>50042</v>
       </c>
       <c r="C14" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D14">
         <v>50041</v>
@@ -7004,7 +8670,7 @@
         <v>50043</v>
       </c>
       <c r="C15" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D15">
         <v>50042</v>
@@ -7030,7 +8696,7 @@
         <v>50044</v>
       </c>
       <c r="C16" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D16">
         <v>50043</v>
@@ -7097,12 +8763,12 @@
       <c r="I1" t="s">
         <v>88</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
       <c r="N1" t="s">
         <v>84</v>
       </c>
@@ -7124,19 +8790,19 @@
         <v>50038</v>
       </c>
       <c r="E2" t="s">
+        <v>187</v>
+      </c>
+      <c r="F2" t="s">
         <v>188</v>
-      </c>
-      <c r="F2" t="s">
-        <v>189</v>
       </c>
       <c r="G2" t="s">
         <v>6</v>
       </c>
       <c r="H2" t="s">
+        <v>189</v>
+      </c>
+      <c r="P2" t="s">
         <v>190</v>
-      </c>
-      <c r="P2" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -7150,19 +8816,19 @@
         <v>50053</v>
       </c>
       <c r="E3" t="s">
+        <v>191</v>
+      </c>
+      <c r="F3" t="s">
         <v>192</v>
-      </c>
-      <c r="F3" t="s">
-        <v>193</v>
       </c>
       <c r="G3" t="s">
         <v>6</v>
       </c>
       <c r="H3" t="s">
+        <v>193</v>
+      </c>
+      <c r="P3" t="s">
         <v>194</v>
-      </c>
-      <c r="P3" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -7176,16 +8842,16 @@
         <v>50054</v>
       </c>
       <c r="E4" t="s">
+        <v>195</v>
+      </c>
+      <c r="F4" t="s">
         <v>196</v>
-      </c>
-      <c r="F4" t="s">
-        <v>197</v>
       </c>
       <c r="G4" t="s">
         <v>6</v>
       </c>
       <c r="H4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -7199,19 +8865,19 @@
         <v>50055</v>
       </c>
       <c r="E5" t="s">
+        <v>198</v>
+      </c>
+      <c r="F5" t="s">
         <v>199</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>200</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
+        <v>189</v>
+      </c>
+      <c r="P5" t="s">
         <v>201</v>
-      </c>
-      <c r="H5" t="s">
-        <v>190</v>
-      </c>
-      <c r="P5" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -7225,19 +8891,19 @@
         <v>50056</v>
       </c>
       <c r="E6" t="s">
+        <v>202</v>
+      </c>
+      <c r="F6" t="s">
         <v>203</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
+        <v>200</v>
+      </c>
+      <c r="H6" t="s">
+        <v>189</v>
+      </c>
+      <c r="P6" t="s">
         <v>204</v>
-      </c>
-      <c r="G6" t="s">
-        <v>201</v>
-      </c>
-      <c r="H6" t="s">
-        <v>190</v>
-      </c>
-      <c r="P6" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -7251,19 +8917,19 @@
         <v>50057</v>
       </c>
       <c r="E7" t="s">
+        <v>205</v>
+      </c>
+      <c r="F7" t="s">
         <v>206</v>
-      </c>
-      <c r="F7" t="s">
-        <v>207</v>
       </c>
       <c r="G7" t="s">
         <v>6</v>
       </c>
       <c r="H7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P7" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -7277,7 +8943,7 @@
         <v>50058</v>
       </c>
       <c r="E8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F8" t="s">
         <v>77</v>
@@ -7286,7 +8952,7 @@
         <v>78</v>
       </c>
       <c r="H8" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -7300,19 +8966,19 @@
         <v>50057</v>
       </c>
       <c r="E9" t="s">
+        <v>272</v>
+      </c>
+      <c r="F9" t="s">
         <v>273</v>
-      </c>
-      <c r="F9" t="s">
-        <v>274</v>
       </c>
       <c r="G9" t="s">
         <v>6</v>
       </c>
       <c r="H9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="P9" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -7326,19 +8992,19 @@
         <v>50060</v>
       </c>
       <c r="E10" t="s">
+        <v>209</v>
+      </c>
+      <c r="F10" t="s">
         <v>210</v>
-      </c>
-      <c r="F10" t="s">
-        <v>211</v>
       </c>
       <c r="G10" t="s">
         <v>6</v>
       </c>
       <c r="H10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -7352,19 +9018,19 @@
         <v>50061</v>
       </c>
       <c r="E11" t="s">
+        <v>212</v>
+      </c>
+      <c r="F11" t="s">
         <v>213</v>
-      </c>
-      <c r="F11" t="s">
-        <v>214</v>
       </c>
       <c r="G11" t="s">
         <v>6</v>
       </c>
       <c r="H11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P11" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -7378,16 +9044,16 @@
         <v>50062</v>
       </c>
       <c r="E12" t="s">
+        <v>215</v>
+      </c>
+      <c r="F12" t="s">
         <v>216</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>217</v>
       </c>
-      <c r="G12" t="s">
-        <v>218</v>
-      </c>
       <c r="H12" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -7401,19 +9067,19 @@
         <v>50063</v>
       </c>
       <c r="E13" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F13" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G13" t="s">
         <v>6</v>
       </c>
       <c r="H13" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P13" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -7427,19 +9093,19 @@
         <v>50064</v>
       </c>
       <c r="E14" t="s">
+        <v>220</v>
+      </c>
+      <c r="F14" t="s">
         <v>221</v>
-      </c>
-      <c r="F14" t="s">
-        <v>222</v>
       </c>
       <c r="G14" t="s">
         <v>6</v>
       </c>
       <c r="H14" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P14" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="15" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -7453,19 +9119,19 @@
         <v>50065</v>
       </c>
       <c r="E15" t="s">
+        <v>223</v>
+      </c>
+      <c r="F15" t="s">
         <v>224</v>
-      </c>
-      <c r="F15" t="s">
-        <v>225</v>
       </c>
       <c r="G15" t="s">
         <v>6</v>
       </c>
       <c r="H15" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P15" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -7479,19 +9145,19 @@
         <v>50066</v>
       </c>
       <c r="E16" t="s">
+        <v>226</v>
+      </c>
+      <c r="F16" t="s">
         <v>227</v>
       </c>
-      <c r="F16" t="s">
+      <c r="G16" t="s">
+        <v>200</v>
+      </c>
+      <c r="H16" t="s">
+        <v>189</v>
+      </c>
+      <c r="P16" t="s">
         <v>228</v>
-      </c>
-      <c r="G16" t="s">
-        <v>201</v>
-      </c>
-      <c r="H16" t="s">
-        <v>190</v>
-      </c>
-      <c r="P16" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="17" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -7505,19 +9171,19 @@
         <v>50067</v>
       </c>
       <c r="E17" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F17" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G17" t="s">
         <v>6</v>
       </c>
       <c r="H17" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P17" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="18" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -7531,19 +9197,19 @@
         <v>50068</v>
       </c>
       <c r="E18" t="s">
+        <v>231</v>
+      </c>
+      <c r="F18" t="s">
         <v>232</v>
-      </c>
-      <c r="F18" t="s">
-        <v>233</v>
       </c>
       <c r="G18" t="s">
         <v>6</v>
       </c>
       <c r="H18" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P18" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="19" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -7557,19 +9223,19 @@
         <v>50069</v>
       </c>
       <c r="E19" t="s">
+        <v>234</v>
+      </c>
+      <c r="F19" t="s">
         <v>235</v>
       </c>
-      <c r="F19" t="s">
+      <c r="G19" t="s">
+        <v>217</v>
+      </c>
+      <c r="H19" t="s">
+        <v>189</v>
+      </c>
+      <c r="P19" t="s">
         <v>236</v>
-      </c>
-      <c r="G19" t="s">
-        <v>218</v>
-      </c>
-      <c r="H19" t="s">
-        <v>190</v>
-      </c>
-      <c r="P19" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="20" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -7583,19 +9249,19 @@
         <v>50070</v>
       </c>
       <c r="E20" t="s">
+        <v>237</v>
+      </c>
+      <c r="F20" t="s">
         <v>238</v>
       </c>
-      <c r="F20" t="s">
+      <c r="G20" t="s">
         <v>239</v>
       </c>
-      <c r="G20" t="s">
+      <c r="H20" t="s">
+        <v>189</v>
+      </c>
+      <c r="P20" t="s">
         <v>240</v>
-      </c>
-      <c r="H20" t="s">
-        <v>190</v>
-      </c>
-      <c r="P20" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="21" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -7609,19 +9275,19 @@
         <v>50071</v>
       </c>
       <c r="E21" t="s">
+        <v>241</v>
+      </c>
+      <c r="F21" t="s">
         <v>242</v>
       </c>
-      <c r="F21" t="s">
+      <c r="G21" t="s">
         <v>243</v>
       </c>
-      <c r="G21" t="s">
+      <c r="H21" t="s">
+        <v>189</v>
+      </c>
+      <c r="P21" t="s">
         <v>244</v>
-      </c>
-      <c r="H21" t="s">
-        <v>190</v>
-      </c>
-      <c r="P21" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="22" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -7635,16 +9301,16 @@
         <v>50072</v>
       </c>
       <c r="E22" t="s">
+        <v>245</v>
+      </c>
+      <c r="F22" t="s">
         <v>246</v>
       </c>
-      <c r="F22" t="s">
-        <v>247</v>
-      </c>
       <c r="G22" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H22" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="23" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -7658,16 +9324,16 @@
         <v>50073</v>
       </c>
       <c r="E23" t="s">
+        <v>247</v>
+      </c>
+      <c r="F23" t="s">
         <v>248</v>
-      </c>
-      <c r="F23" t="s">
-        <v>249</v>
       </c>
       <c r="G23" t="s">
         <v>6</v>
       </c>
       <c r="H23" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="24" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -7681,16 +9347,16 @@
         <v>50074</v>
       </c>
       <c r="E24" t="s">
+        <v>249</v>
+      </c>
+      <c r="F24" t="s">
         <v>250</v>
-      </c>
-      <c r="F24" t="s">
-        <v>251</v>
       </c>
       <c r="G24" t="s">
         <v>6</v>
       </c>
       <c r="H24" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="25" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -7704,19 +9370,19 @@
         <v>50075</v>
       </c>
       <c r="E25" t="s">
+        <v>251</v>
+      </c>
+      <c r="F25" t="s">
         <v>252</v>
       </c>
-      <c r="F25" t="s">
+      <c r="G25" t="s">
+        <v>200</v>
+      </c>
+      <c r="H25" t="s">
+        <v>189</v>
+      </c>
+      <c r="P25" t="s">
         <v>253</v>
-      </c>
-      <c r="G25" t="s">
-        <v>201</v>
-      </c>
-      <c r="H25" t="s">
-        <v>190</v>
-      </c>
-      <c r="P25" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="26" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -7730,16 +9396,16 @@
         <v>50076</v>
       </c>
       <c r="E26" t="s">
+        <v>254</v>
+      </c>
+      <c r="F26" t="s">
         <v>255</v>
-      </c>
-      <c r="F26" t="s">
-        <v>256</v>
       </c>
       <c r="G26" t="s">
         <v>6</v>
       </c>
       <c r="H26" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="27" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -7753,16 +9419,16 @@
         <v>50077</v>
       </c>
       <c r="E27" t="s">
+        <v>274</v>
+      </c>
+      <c r="F27" t="s">
         <v>275</v>
       </c>
-      <c r="F27" t="s">
+      <c r="G27" t="s">
         <v>276</v>
       </c>
-      <c r="G27" t="s">
-        <v>277</v>
-      </c>
       <c r="H27" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="28" spans="1:16" ht="115.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -7776,16 +9442,16 @@
         <v>50078</v>
       </c>
       <c r="E28" t="s">
+        <v>256</v>
+      </c>
+      <c r="F28" t="s">
         <v>257</v>
-      </c>
-      <c r="F28" t="s">
-        <v>258</v>
       </c>
       <c r="G28" t="s">
         <v>96</v>
       </c>
       <c r="H28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -7800,19 +9466,907 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P31"/>
+  <dimension ref="A1:K33"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="6" width="18.375" customWidth="1"/>
+    <col min="9" max="9" width="24.125" customWidth="1"/>
+    <col min="11" max="11" width="27.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>277</v>
+      </c>
+      <c r="B1" t="s">
+        <v>278</v>
+      </c>
+      <c r="C1" t="s">
+        <v>279</v>
+      </c>
+      <c r="E1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1" t="s">
+        <v>281</v>
+      </c>
+      <c r="J1" t="s">
+        <v>282</v>
+      </c>
+      <c r="K1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="57.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>50080</v>
+      </c>
+      <c r="C2">
+        <v>50037</v>
+      </c>
+      <c r="D2" s="3"/>
+      <c r="E2" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="G2" t="s">
+        <v>284</v>
+      </c>
+      <c r="H2" t="s">
+        <v>285</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="57.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>50081</v>
+      </c>
+      <c r="C3">
+        <v>50080</v>
+      </c>
+      <c r="D3" s="3"/>
+      <c r="E3" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="G3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" t="s">
+        <v>285</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="K3" s="2"/>
+    </row>
+    <row r="4" spans="1:11" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>50082</v>
+      </c>
+      <c r="C4">
+        <v>50081</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="G4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H4" t="s">
+        <v>285</v>
+      </c>
+      <c r="I4" s="2"/>
+      <c r="K4" s="2"/>
+    </row>
+    <row r="5" spans="1:11" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>50083</v>
+      </c>
+      <c r="C5">
+        <v>50082</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="G5" t="s">
+        <v>291</v>
+      </c>
+      <c r="H5" t="s">
+        <v>285</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>50084</v>
+      </c>
+      <c r="C6">
+        <v>50080</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="G6" t="s">
+        <v>6</v>
+      </c>
+      <c r="H6" t="s">
+        <v>285</v>
+      </c>
+      <c r="I6" s="2"/>
+      <c r="K6" s="2"/>
+    </row>
+    <row r="7" spans="1:11" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>50085</v>
+      </c>
+      <c r="C7">
+        <v>50084</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="G7" t="s">
+        <v>284</v>
+      </c>
+      <c r="H7" t="s">
+        <v>285</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="K7" s="2"/>
+    </row>
+    <row r="8" spans="1:11" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>50086</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="G8" t="s">
+        <v>20</v>
+      </c>
+      <c r="H8" t="s">
+        <v>285</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="K8" s="2"/>
+    </row>
+    <row r="9" spans="1:11" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>50087</v>
+      </c>
+      <c r="C9">
+        <v>50086</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="G9" t="s">
+        <v>6</v>
+      </c>
+      <c r="H9" t="s">
+        <v>285</v>
+      </c>
+      <c r="I9" s="2"/>
+      <c r="K9" s="2"/>
+    </row>
+    <row r="10" spans="1:11" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>50088</v>
+      </c>
+      <c r="C10">
+        <v>50087</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="G10" t="s">
+        <v>284</v>
+      </c>
+      <c r="H10" t="s">
+        <v>285</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>50089</v>
+      </c>
+      <c r="C11">
+        <v>50085</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="G11" t="s">
+        <v>6</v>
+      </c>
+      <c r="H11" t="s">
+        <v>285</v>
+      </c>
+      <c r="I11" s="2"/>
+      <c r="K11" s="2"/>
+    </row>
+    <row r="12" spans="1:11" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>50090</v>
+      </c>
+      <c r="C12">
+        <v>50085</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="G12" t="s">
+        <v>304</v>
+      </c>
+      <c r="H12" t="s">
+        <v>285</v>
+      </c>
+      <c r="I12" s="2"/>
+      <c r="K12" s="2"/>
+    </row>
+    <row r="13" spans="1:11" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>50091</v>
+      </c>
+      <c r="C13">
+        <v>50090</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="G13" t="s">
+        <v>307</v>
+      </c>
+      <c r="H13" t="s">
+        <v>285</v>
+      </c>
+      <c r="I13" s="2"/>
+      <c r="K13" s="2"/>
+    </row>
+    <row r="14" spans="1:11" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>50092</v>
+      </c>
+      <c r="C14">
+        <v>50091</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="G14" t="s">
+        <v>309</v>
+      </c>
+      <c r="H14" t="s">
+        <v>285</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>50093</v>
+      </c>
+      <c r="C15">
+        <v>50092</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="G15" t="s">
+        <v>307</v>
+      </c>
+      <c r="H15" t="s">
+        <v>285</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="K15" s="2"/>
+    </row>
+    <row r="16" spans="1:11" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>50094</v>
+      </c>
+      <c r="C16">
+        <v>50093</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="G16" t="s">
+        <v>317</v>
+      </c>
+      <c r="H16" t="s">
+        <v>285</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="K16" s="2"/>
+    </row>
+    <row r="17" spans="1:11" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>50095</v>
+      </c>
+      <c r="C17">
+        <v>50089</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="G17" t="s">
+        <v>304</v>
+      </c>
+      <c r="H17" t="s">
+        <v>285</v>
+      </c>
+      <c r="I17" s="2"/>
+      <c r="K17" s="2"/>
+    </row>
+    <row r="18" spans="1:11" ht="57.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>50096</v>
+      </c>
+      <c r="C18">
+        <v>50095</v>
+      </c>
+      <c r="D18" s="3"/>
+      <c r="E18" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="G18" t="s">
+        <v>320</v>
+      </c>
+      <c r="H18" t="s">
+        <v>285</v>
+      </c>
+      <c r="I18" s="2"/>
+      <c r="K18" s="2" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="57.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>50097</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="D19" s="3"/>
+      <c r="E19" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="H19" t="s">
+        <v>285</v>
+      </c>
+      <c r="I19" s="2"/>
+      <c r="K19" s="2"/>
+    </row>
+    <row r="20" spans="1:11" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>50098</v>
+      </c>
+      <c r="C20">
+        <v>50096</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="G20" t="s">
+        <v>304</v>
+      </c>
+      <c r="H20" t="s">
+        <v>285</v>
+      </c>
+      <c r="I20" s="2"/>
+      <c r="K20" s="2"/>
+    </row>
+    <row r="21" spans="1:11" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>50099</v>
+      </c>
+      <c r="C21">
+        <v>50098</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="G21" t="s">
+        <v>325</v>
+      </c>
+      <c r="H21" t="s">
+        <v>369</v>
+      </c>
+      <c r="I21" s="2"/>
+      <c r="K21" s="2"/>
+    </row>
+    <row r="22" spans="1:11" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <v>50100</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="G22" t="s">
+        <v>320</v>
+      </c>
+      <c r="H22" t="s">
+        <v>285</v>
+      </c>
+      <c r="I22" s="2"/>
+      <c r="K22" s="2" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="58.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <v>50101</v>
+      </c>
+      <c r="C23">
+        <v>50099</v>
+      </c>
+      <c r="D23" s="3"/>
+      <c r="E23" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="H23" t="s">
+        <v>285</v>
+      </c>
+      <c r="I23" s="2"/>
+      <c r="K23" s="2"/>
+    </row>
+    <row r="24" spans="1:11" ht="58.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24">
+        <v>50102</v>
+      </c>
+      <c r="C24">
+        <v>50100</v>
+      </c>
+      <c r="D24" s="3"/>
+      <c r="E24" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="G24" t="s">
+        <v>320</v>
+      </c>
+      <c r="H24" t="s">
+        <v>285</v>
+      </c>
+      <c r="I24" s="2"/>
+      <c r="K24" s="2" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>26</v>
+      </c>
+      <c r="B25">
+        <v>50103</v>
+      </c>
+      <c r="C25">
+        <v>50101</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="G25" t="s">
+        <v>304</v>
+      </c>
+      <c r="H25" t="s">
+        <v>285</v>
+      </c>
+      <c r="I25" s="2"/>
+      <c r="K25" s="2"/>
+    </row>
+    <row r="26" spans="1:11" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>27</v>
+      </c>
+      <c r="B26">
+        <v>50104</v>
+      </c>
+      <c r="C26">
+        <v>50103</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="G26" t="s">
+        <v>320</v>
+      </c>
+      <c r="H26" t="s">
+        <v>285</v>
+      </c>
+      <c r="I26" s="2"/>
+      <c r="K26" s="2"/>
+    </row>
+    <row r="27" spans="1:11" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>28</v>
+      </c>
+      <c r="B27">
+        <v>50105</v>
+      </c>
+      <c r="C27">
+        <v>50104</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="G27" t="s">
+        <v>304</v>
+      </c>
+      <c r="H27" t="s">
+        <v>285</v>
+      </c>
+      <c r="I27" s="2"/>
+      <c r="K27" s="2"/>
+    </row>
+    <row r="28" spans="1:11" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>29</v>
+      </c>
+      <c r="B28">
+        <v>50106</v>
+      </c>
+      <c r="C28">
+        <v>50104</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="G28" t="s">
+        <v>304</v>
+      </c>
+      <c r="H28" t="s">
+        <v>285</v>
+      </c>
+      <c r="I28" s="2"/>
+      <c r="K28" s="2"/>
+    </row>
+    <row r="29" spans="1:11" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>30</v>
+      </c>
+      <c r="B29">
+        <v>50107</v>
+      </c>
+      <c r="C29">
+        <v>50106</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="F29" s="2"/>
+      <c r="G29" t="s">
+        <v>335</v>
+      </c>
+      <c r="H29" t="s">
+        <v>285</v>
+      </c>
+      <c r="I29" s="2"/>
+      <c r="K29" s="2"/>
+    </row>
+    <row r="30" spans="1:11" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>31</v>
+      </c>
+      <c r="B30">
+        <v>50130</v>
+      </c>
+      <c r="C30">
+        <v>50126</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="G30" t="s">
+        <v>320</v>
+      </c>
+      <c r="H30" t="s">
+        <v>124</v>
+      </c>
+      <c r="I30" s="2"/>
+      <c r="K30" s="2" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>32</v>
+      </c>
+      <c r="B31">
+        <v>50131</v>
+      </c>
+      <c r="C31">
+        <v>50130</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="G31" t="s">
+        <v>338</v>
+      </c>
+      <c r="H31" t="s">
+        <v>388</v>
+      </c>
+      <c r="I31" s="2"/>
+      <c r="K31" s="2"/>
+    </row>
+    <row r="32" spans="1:11" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>33</v>
+      </c>
+      <c r="B32">
+        <v>50132</v>
+      </c>
+      <c r="C32">
+        <v>50131</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="G32" t="s">
+        <v>338</v>
+      </c>
+      <c r="H32" t="s">
+        <v>388</v>
+      </c>
+      <c r="I32" s="2"/>
+      <c r="K32" s="2"/>
+    </row>
+    <row r="33" spans="1:11" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <v>34</v>
+      </c>
+      <c r="B33">
+        <v>50133</v>
+      </c>
+      <c r="C33">
+        <v>50132</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="G33" t="s">
+        <v>338</v>
+      </c>
+      <c r="H33" t="s">
+        <v>388</v>
+      </c>
+      <c r="I33" s="2"/>
+      <c r="K33" s="2"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="D23:D24"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:K27"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="3" width="9" customWidth="1"/>
     <col min="4" max="4" width="18.875" customWidth="1"/>
     <col min="5" max="5" width="18.625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="32.125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="18.625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="81.375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="24.5" customWidth="1"/>
+    <col min="10" max="10" width="18.625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="81.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>82</v>
       </c>
@@ -7835,930 +10389,566 @@
         <v>87</v>
       </c>
       <c r="I1" t="s">
-        <v>88</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" t="s">
-        <v>84</v>
-      </c>
-      <c r="O1" t="s">
+        <v>281</v>
+      </c>
+      <c r="J1" t="s">
         <v>85</v>
       </c>
-      <c r="P1" t="s">
+      <c r="K1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>50080</v>
+        <v>50108</v>
       </c>
       <c r="C2">
-        <v>50037</v>
+        <v>50105</v>
       </c>
       <c r="E2" t="s">
-        <v>330</v>
+        <v>389</v>
       </c>
       <c r="F2" t="s">
-        <v>281</v>
+        <v>409</v>
       </c>
       <c r="G2" t="s">
-        <v>96</v>
+        <v>6</v>
       </c>
       <c r="H2" t="s">
-        <v>125</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>124</v>
+      </c>
+      <c r="I2" s="2"/>
+    </row>
+    <row r="3" spans="1:11" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>50081</v>
+        <v>50109</v>
       </c>
       <c r="C3">
-        <v>50080</v>
+        <v>50108</v>
       </c>
       <c r="E3" t="s">
-        <v>334</v>
+        <v>431</v>
       </c>
       <c r="F3" t="s">
-        <v>280</v>
+        <v>432</v>
       </c>
       <c r="G3" t="s">
-        <v>6</v>
+        <v>422</v>
       </c>
       <c r="H3" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>124</v>
+      </c>
+      <c r="I3" s="2"/>
+    </row>
+    <row r="4" spans="1:11" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4">
-        <v>50082</v>
+        <v>50110</v>
       </c>
       <c r="C4">
-        <v>50081</v>
+        <v>50109</v>
       </c>
       <c r="E4" t="s">
-        <v>333</v>
+        <v>390</v>
       </c>
       <c r="F4" t="s">
-        <v>282</v>
+        <v>410</v>
       </c>
       <c r="G4" t="s">
-        <v>278</v>
+        <v>420</v>
       </c>
       <c r="H4" t="s">
-        <v>125</v>
-      </c>
-      <c r="P4" s="3" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>124</v>
+      </c>
+      <c r="I4" s="2"/>
+    </row>
+    <row r="5" spans="1:11" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5">
-        <v>50083</v>
+        <v>50111</v>
       </c>
       <c r="C5">
-        <v>50085</v>
+        <v>50110</v>
       </c>
       <c r="E5" t="s">
-        <v>279</v>
+        <v>391</v>
       </c>
       <c r="F5" t="s">
-        <v>285</v>
+        <v>433</v>
       </c>
       <c r="G5" t="s">
-        <v>6</v>
+        <v>421</v>
       </c>
       <c r="H5" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>124</v>
+      </c>
+      <c r="I5" s="2"/>
+    </row>
+    <row r="6" spans="1:11" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6">
-        <v>50084</v>
+        <v>50112</v>
       </c>
       <c r="C6">
-        <v>50083</v>
+        <v>50111</v>
       </c>
       <c r="E6" t="s">
-        <v>286</v>
+        <v>411</v>
       </c>
       <c r="F6" t="s">
-        <v>287</v>
+        <v>434</v>
       </c>
       <c r="G6" t="s">
-        <v>288</v>
+        <v>423</v>
       </c>
       <c r="H6" t="s">
-        <v>125</v>
-      </c>
-      <c r="P6" s="3" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>124</v>
+      </c>
+      <c r="I6" s="2"/>
+    </row>
+    <row r="7" spans="1:11" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7">
-        <v>50085</v>
+        <v>50113</v>
       </c>
       <c r="C7">
-        <v>50080</v>
+        <v>50112</v>
       </c>
       <c r="E7" t="s">
-        <v>335</v>
+        <v>392</v>
       </c>
       <c r="F7" t="s">
-        <v>290</v>
+        <v>435</v>
       </c>
       <c r="G7" t="s">
-        <v>6</v>
+        <v>424</v>
       </c>
       <c r="H7" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>124</v>
+      </c>
+      <c r="I7" s="2"/>
+    </row>
+    <row r="8" spans="1:11" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8">
-        <v>50086</v>
+        <v>50114</v>
       </c>
       <c r="C8">
-        <v>50085</v>
+        <v>50113</v>
       </c>
       <c r="E8" t="s">
-        <v>336</v>
+        <v>393</v>
+      </c>
+      <c r="F8" t="s">
+        <v>436</v>
       </c>
       <c r="G8" t="s">
-        <v>96</v>
+        <v>425</v>
       </c>
       <c r="H8" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>124</v>
+      </c>
+      <c r="I8" s="2"/>
+    </row>
+    <row r="9" spans="1:11" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9">
-        <v>50087</v>
+        <v>50115</v>
       </c>
       <c r="C9">
-        <v>50086</v>
+        <v>50114</v>
       </c>
       <c r="E9" t="s">
-        <v>291</v>
+        <v>394</v>
+      </c>
+      <c r="F9" t="s">
+        <v>432</v>
       </c>
       <c r="G9" t="s">
-        <v>6</v>
+        <v>422</v>
       </c>
       <c r="H9" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>124</v>
+      </c>
+      <c r="I9" s="2"/>
+    </row>
+    <row r="10" spans="1:11" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10">
-        <v>50088</v>
+        <v>50116</v>
       </c>
       <c r="C10">
-        <v>50087</v>
+        <v>50115</v>
       </c>
       <c r="E10" t="s">
-        <v>292</v>
+        <v>395</v>
+      </c>
+      <c r="F10" t="s">
+        <v>412</v>
       </c>
       <c r="G10" t="s">
         <v>6</v>
       </c>
       <c r="H10" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>124</v>
+      </c>
+      <c r="I10" s="2"/>
+    </row>
+    <row r="11" spans="1:11" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11">
-        <v>50089</v>
+        <v>50117</v>
       </c>
       <c r="C11">
-        <v>50088</v>
+        <v>50116</v>
       </c>
       <c r="E11" t="s">
-        <v>293</v>
+        <v>396</v>
+      </c>
+      <c r="F11" t="s">
+        <v>432</v>
       </c>
       <c r="G11" t="s">
-        <v>298</v>
-      </c>
-      <c r="H11" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>422</v>
+      </c>
+      <c r="I11" s="2"/>
+    </row>
+    <row r="12" spans="1:11" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12">
-        <v>50090</v>
+        <v>50118</v>
       </c>
       <c r="C12">
-        <v>50088</v>
+        <v>50117</v>
       </c>
       <c r="E12" t="s">
-        <v>294</v>
+        <v>397</v>
       </c>
       <c r="F12" t="s">
-        <v>296</v>
+        <v>432</v>
       </c>
       <c r="G12" t="s">
-        <v>277</v>
-      </c>
-      <c r="H12" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>423</v>
+      </c>
+      <c r="I12" s="2"/>
+    </row>
+    <row r="13" spans="1:11" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13">
-        <v>50091</v>
+        <v>50119</v>
       </c>
       <c r="C13">
-        <v>50090</v>
+        <v>50118</v>
       </c>
       <c r="E13" t="s">
-        <v>295</v>
+        <v>398</v>
       </c>
       <c r="F13" t="s">
-        <v>299</v>
+        <v>413</v>
       </c>
       <c r="G13" t="s">
-        <v>307</v>
-      </c>
-      <c r="H13" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>426</v>
+      </c>
+      <c r="I13" s="2"/>
+    </row>
+    <row r="14" spans="1:11" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14">
-        <v>50092</v>
+        <v>50120</v>
       </c>
       <c r="C14">
-        <v>50091</v>
+        <v>50119</v>
       </c>
       <c r="E14" t="s">
-        <v>297</v>
+        <v>399</v>
       </c>
       <c r="F14" t="s">
-        <v>300</v>
+        <v>414</v>
       </c>
       <c r="G14" t="s">
-        <v>96</v>
-      </c>
-      <c r="H14" t="s">
-        <v>125</v>
-      </c>
-      <c r="P14" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>426</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15">
-        <v>50093</v>
+        <v>50121</v>
       </c>
       <c r="C15">
-        <v>50092</v>
+        <v>50120</v>
       </c>
       <c r="E15" t="s">
-        <v>302</v>
+        <v>400</v>
       </c>
       <c r="F15" t="s">
-        <v>303</v>
+        <v>415</v>
       </c>
       <c r="G15" t="s">
-        <v>308</v>
-      </c>
-      <c r="H15" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>427</v>
+      </c>
+      <c r="I15" s="2"/>
+    </row>
+    <row r="16" spans="1:11" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16">
-        <v>50094</v>
+        <v>50122</v>
       </c>
       <c r="C16">
-        <v>50093</v>
+        <v>50121</v>
       </c>
       <c r="E16" t="s">
-        <v>304</v>
+        <v>401</v>
+      </c>
+      <c r="F16" t="s">
+        <v>437</v>
       </c>
       <c r="G16" t="s">
-        <v>306</v>
-      </c>
-      <c r="H16" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>428</v>
+      </c>
+      <c r="I16" s="2"/>
+    </row>
+    <row r="17" spans="1:9" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17">
-        <v>50095</v>
+        <v>50123</v>
       </c>
       <c r="C17">
-        <v>50094</v>
+        <v>50122</v>
       </c>
       <c r="E17" t="s">
-        <v>326</v>
+        <v>402</v>
       </c>
       <c r="F17" t="s">
-        <v>305</v>
+        <v>432</v>
       </c>
       <c r="G17" t="s">
-        <v>96</v>
-      </c>
-      <c r="H17" t="s">
-        <v>125</v>
-      </c>
-      <c r="P17" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>423</v>
+      </c>
+      <c r="I17" s="2"/>
+    </row>
+    <row r="18" spans="1:9" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18">
-        <v>50096</v>
+        <v>50124</v>
       </c>
       <c r="C18">
-        <v>50095</v>
+        <v>50123</v>
       </c>
       <c r="E18" t="s">
-        <v>309</v>
+        <v>404</v>
+      </c>
+      <c r="F18" t="s">
+        <v>416</v>
       </c>
       <c r="G18" t="s">
-        <v>277</v>
-      </c>
-      <c r="H18" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>426</v>
+      </c>
+      <c r="I18" s="2"/>
+    </row>
+    <row r="19" spans="1:9" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19">
-        <v>50097</v>
+        <v>50125</v>
       </c>
       <c r="C19">
-        <v>50096</v>
+        <v>50124</v>
       </c>
       <c r="E19" t="s">
-        <v>311</v>
+        <v>403</v>
       </c>
       <c r="G19" t="s">
-        <v>109</v>
-      </c>
-      <c r="H19" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>429</v>
+      </c>
+      <c r="I19" s="2"/>
+    </row>
+    <row r="20" spans="1:9" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20">
-        <v>50098</v>
+        <v>50126</v>
       </c>
       <c r="C20">
-        <v>50097</v>
+        <v>50124</v>
       </c>
       <c r="E20" t="s">
-        <v>312</v>
+        <v>408</v>
+      </c>
+      <c r="F20" t="s">
+        <v>432</v>
       </c>
       <c r="G20" t="s">
-        <v>96</v>
-      </c>
-      <c r="H20" t="s">
-        <v>125</v>
-      </c>
-      <c r="P20" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>423</v>
+      </c>
+      <c r="I20" s="2"/>
+    </row>
+    <row r="21" spans="1:9" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21">
-        <v>50099</v>
+        <v>50127</v>
       </c>
       <c r="C21">
-        <v>50098</v>
+        <v>50122</v>
       </c>
       <c r="E21" t="s">
-        <v>327</v>
+        <v>405</v>
       </c>
       <c r="F21" t="s">
-        <v>328</v>
+        <v>417</v>
       </c>
       <c r="G21" t="s">
-        <v>96</v>
-      </c>
-      <c r="H21" t="s">
-        <v>125</v>
-      </c>
-      <c r="P21" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>426</v>
+      </c>
+      <c r="I21" s="2"/>
+    </row>
+    <row r="22" spans="1:9" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22">
-        <v>50100</v>
+        <v>50128</v>
       </c>
       <c r="C22">
-        <v>50099</v>
+        <v>50127</v>
       </c>
       <c r="E22" t="s">
-        <v>329</v>
+        <v>406</v>
+      </c>
+      <c r="F22" t="s">
+        <v>418</v>
       </c>
       <c r="G22" t="s">
-        <v>277</v>
-      </c>
-      <c r="H22" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>426</v>
+      </c>
+      <c r="I22" s="2"/>
+    </row>
+    <row r="23" spans="1:9" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23">
-        <v>50101</v>
+        <v>50129</v>
       </c>
       <c r="C23">
-        <v>50100</v>
+        <v>50128</v>
       </c>
       <c r="E23" t="s">
-        <v>332</v>
+        <v>407</v>
+      </c>
+      <c r="F23" t="s">
+        <v>419</v>
       </c>
       <c r="G23" t="s">
-        <v>96</v>
-      </c>
-      <c r="H23" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>430</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24">
-        <v>50102</v>
+        <v>50130</v>
       </c>
       <c r="C24">
-        <v>50101</v>
+        <v>50122</v>
       </c>
       <c r="E24" t="s">
-        <v>316</v>
-      </c>
-      <c r="G24" t="s">
-        <v>277</v>
-      </c>
-      <c r="H24" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>395</v>
+      </c>
+      <c r="F24" t="s">
+        <v>432</v>
+      </c>
+      <c r="I24" s="2"/>
+    </row>
+    <row r="25" spans="1:9" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25">
-        <v>50103</v>
+        <v>50131</v>
       </c>
       <c r="C25">
-        <v>50102</v>
+        <v>50130</v>
       </c>
       <c r="E25" t="s">
-        <v>331</v>
-      </c>
-      <c r="G25" t="s">
-        <v>96</v>
-      </c>
-      <c r="H25" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>445</v>
+      </c>
+      <c r="F25" t="s">
+        <v>413</v>
+      </c>
+      <c r="I25" s="2"/>
+    </row>
+    <row r="26" spans="1:9" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26">
-        <v>50104</v>
+        <v>50132</v>
       </c>
       <c r="C26">
-        <v>50103</v>
+        <v>50131</v>
       </c>
       <c r="E26" t="s">
-        <v>317</v>
-      </c>
-      <c r="G26" t="s">
-        <v>277</v>
-      </c>
-      <c r="H26" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27">
-        <v>26</v>
-      </c>
-      <c r="B27">
-        <v>50105</v>
-      </c>
-      <c r="C27">
-        <v>50104</v>
-      </c>
-      <c r="E27" t="s">
-        <v>318</v>
-      </c>
-      <c r="G27" t="s">
-        <v>277</v>
-      </c>
-      <c r="H27" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28">
-        <v>27</v>
-      </c>
-      <c r="B28">
-        <v>50106</v>
-      </c>
-      <c r="C28">
-        <v>50105</v>
-      </c>
-      <c r="E28" t="s">
-        <v>319</v>
-      </c>
-      <c r="G28" t="s">
-        <v>320</v>
-      </c>
-      <c r="H28" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29">
-        <v>28</v>
-      </c>
-      <c r="B29">
-        <v>50107</v>
-      </c>
-      <c r="E29" t="s">
-        <v>337</v>
-      </c>
-      <c r="F29" t="s">
-        <v>282</v>
-      </c>
-      <c r="G29" t="s">
-        <v>288</v>
-      </c>
-      <c r="H29" t="s">
-        <v>324</v>
-      </c>
-      <c r="P29" s="3" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30">
-        <v>29</v>
-      </c>
-      <c r="B30">
-        <v>50108</v>
-      </c>
-      <c r="C30">
-        <v>50107</v>
-      </c>
-      <c r="E30" t="s">
-        <v>315</v>
-      </c>
-      <c r="G30" t="s">
-        <v>322</v>
-      </c>
-      <c r="H30" t="s">
-        <v>323</v>
-      </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31">
-        <v>30</v>
-      </c>
-      <c r="B31">
-        <v>50109</v>
-      </c>
-      <c r="C31">
-        <v>50108</v>
-      </c>
-      <c r="E31" t="s">
-        <v>321</v>
-      </c>
-      <c r="G31" t="s">
-        <v>322</v>
-      </c>
-      <c r="H31" t="s">
-        <v>323</v>
-      </c>
-      <c r="P31" s="3"/>
+        <v>446</v>
+      </c>
+      <c r="F26" t="s">
+        <v>447</v>
+      </c>
+      <c r="I26" s="2"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I27" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P11"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="3" width="9" customWidth="1"/>
-    <col min="4" max="4" width="18.875" customWidth="1"/>
-    <col min="5" max="5" width="18.625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="32.125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="18.625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="81.375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B1" t="s">
-        <v>83</v>
-      </c>
-      <c r="C1" t="s">
-        <v>105</v>
-      </c>
-      <c r="E1" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H1" t="s">
-        <v>87</v>
-      </c>
-      <c r="I1" t="s">
-        <v>88</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" t="s">
-        <v>84</v>
-      </c>
-      <c r="O1" t="s">
-        <v>85</v>
-      </c>
-      <c r="P1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>50045</v>
-      </c>
-      <c r="C2">
-        <v>50038</v>
-      </c>
-      <c r="E2" t="s">
-        <v>112</v>
-      </c>
-      <c r="G2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>50046</v>
-      </c>
-      <c r="E3" t="s">
-        <v>113</v>
-      </c>
-      <c r="G3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H3" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>50047</v>
-      </c>
-      <c r="E4" t="s">
-        <v>114</v>
-      </c>
-      <c r="G4" t="s">
-        <v>6</v>
-      </c>
-      <c r="H4" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <v>50048</v>
-      </c>
-      <c r="E5" t="s">
-        <v>115</v>
-      </c>
-      <c r="G5" t="s">
-        <v>6</v>
-      </c>
-      <c r="H5" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>50049</v>
-      </c>
-      <c r="E6" t="s">
-        <v>116</v>
-      </c>
-      <c r="G6" t="s">
-        <v>6</v>
-      </c>
-      <c r="H6" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>50050</v>
-      </c>
-      <c r="E7" t="s">
-        <v>117</v>
-      </c>
-      <c r="G7" t="s">
-        <v>6</v>
-      </c>
-      <c r="H7" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8">
-        <v>50051</v>
-      </c>
-      <c r="E8" t="s">
-        <v>118</v>
-      </c>
-      <c r="G8" t="s">
-        <v>6</v>
-      </c>
-      <c r="H8" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9">
-        <v>50052</v>
-      </c>
-      <c r="E9" t="s">
-        <v>119</v>
-      </c>
-      <c r="G9" t="s">
-        <v>6</v>
-      </c>
-      <c r="H9" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10">
-        <v>50053</v>
-      </c>
-      <c r="E10" t="s">
-        <v>120</v>
-      </c>
-      <c r="G10" t="s">
-        <v>6</v>
-      </c>
-      <c r="H10" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11">
-        <v>50054</v>
-      </c>
-      <c r="E11" t="s">
-        <v>121</v>
-      </c>
-      <c r="G11" t="s">
-        <v>96</v>
-      </c>
-      <c r="H11" t="s">
-        <v>125</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -8801,12 +10991,12 @@
       <c r="I1" t="s">
         <v>88</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
       <c r="N1" t="s">
         <v>84</v>
       </c>
@@ -8834,7 +11024,7 @@
         <v>6</v>
       </c>
       <c r="H2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -8851,7 +11041,7 @@
         <v>6</v>
       </c>
       <c r="H3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -8868,7 +11058,7 @@
         <v>6</v>
       </c>
       <c r="H4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -8885,7 +11075,7 @@
         <v>6</v>
       </c>
       <c r="H5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -8902,7 +11092,7 @@
         <v>6</v>
       </c>
       <c r="H6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -8919,7 +11109,7 @@
         <v>6</v>
       </c>
       <c r="H7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -8936,7 +11126,7 @@
         <v>6</v>
       </c>
       <c r="H8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -8953,7 +11143,7 @@
         <v>6</v>
       </c>
       <c r="H9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -8970,7 +11160,7 @@
         <v>6</v>
       </c>
       <c r="H10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -8987,7 +11177,7 @@
         <v>96</v>
       </c>
       <c r="H11" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -9038,12 +11228,12 @@
       <c r="I1" t="s">
         <v>88</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
       <c r="N1" t="s">
         <v>84</v>
       </c>
@@ -9071,7 +11261,7 @@
         <v>6</v>
       </c>
       <c r="H2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -9088,7 +11278,7 @@
         <v>6</v>
       </c>
       <c r="H3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -9105,7 +11295,7 @@
         <v>6</v>
       </c>
       <c r="H4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -9122,7 +11312,7 @@
         <v>6</v>
       </c>
       <c r="H5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -9139,7 +11329,7 @@
         <v>6</v>
       </c>
       <c r="H6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -9156,7 +11346,7 @@
         <v>6</v>
       </c>
       <c r="H7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -9173,7 +11363,7 @@
         <v>6</v>
       </c>
       <c r="H8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -9190,7 +11380,7 @@
         <v>6</v>
       </c>
       <c r="H9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -9207,7 +11397,7 @@
         <v>6</v>
       </c>
       <c r="H10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -9224,7 +11414,7 @@
         <v>96</v>
       </c>
       <c r="H11" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -9234,4 +11424,175 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="4" max="4" width="18.125" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="26.875" customWidth="1"/>
+    <col min="9" max="9" width="26.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>352</v>
+      </c>
+      <c r="B1" t="s">
+        <v>353</v>
+      </c>
+      <c r="C1" t="s">
+        <v>354</v>
+      </c>
+      <c r="E1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" t="s">
+        <v>355</v>
+      </c>
+      <c r="I1" t="s">
+        <v>281</v>
+      </c>
+      <c r="J1" t="s">
+        <v>356</v>
+      </c>
+      <c r="K1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>59000</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="G2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2">
+        <v>99</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>59001</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="G3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H3" t="s">
+        <v>448</v>
+      </c>
+      <c r="I3" s="2"/>
+    </row>
+    <row r="4" spans="1:11" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>59002</v>
+      </c>
+      <c r="C4">
+        <v>59001</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="G4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" t="s">
+        <v>448</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>59003</v>
+      </c>
+      <c r="C5">
+        <v>59002</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="G5" t="s">
+        <v>200</v>
+      </c>
+      <c r="H5" t="s">
+        <v>448</v>
+      </c>
+      <c r="I5" s="2"/>
+    </row>
+    <row r="6" spans="1:11" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>59004</v>
+      </c>
+      <c r="C6">
+        <v>59003</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="G6" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" t="s">
+        <v>448</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>
--- a/01_기획/02. 컨텐츠/컨텐츠_맵 설정.xlsx
+++ b/01_기획/02. 컨텐츠/컨텐츠_맵 설정.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="14385" yWindow="-15" windowWidth="14430" windowHeight="12060" tabRatio="687" firstSheet="1" activeTab="8"/>
+    <workbookView xWindow="14385" yWindow="-15" windowWidth="14430" windowHeight="12060" tabRatio="687" firstSheet="1" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="튜토리얼" sheetId="5" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="810" uniqueCount="449">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="812" uniqueCount="449">
   <si>
     <t>제목</t>
   </si>
@@ -1115,10 +1115,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Movie</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>남쪽 숲으로</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1537,6 +1533,9 @@
   <si>
     <t>SS</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">보물 위에 가만히 서 있으면 보상을 받을 수 있습니다. </t>
   </si>
 </sst>
 </file>
@@ -9522,7 +9521,7 @@
         <v>283</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="G2" t="s">
         <v>284</v>
@@ -9552,7 +9551,7 @@
         <v>288</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="G3" t="s">
         <v>20</v>
@@ -9576,10 +9575,10 @@
         <v>50081</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="G4" t="s">
         <v>6</v>
@@ -9604,7 +9603,7 @@
         <v>290</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="G5" t="s">
         <v>291</v>
@@ -9633,7 +9632,7 @@
         <v>297</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="G6" t="s">
         <v>6</v>
@@ -9658,7 +9657,7 @@
         <v>298</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="G7" t="s">
         <v>284</v>
@@ -9679,13 +9678,13 @@
         <v>50086</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>300</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="G8" t="s">
         <v>20</v>
@@ -9709,10 +9708,10 @@
         <v>50086</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="G9" t="s">
         <v>6</v>
@@ -9737,7 +9736,7 @@
         <v>294</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="G10" t="s">
         <v>284</v>
@@ -9763,7 +9762,7 @@
         <v>50085</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>302</v>
@@ -9788,7 +9787,7 @@
         <v>50085</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>305</v>
@@ -9813,7 +9812,7 @@
         <v>50090</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>306</v>
@@ -9841,7 +9840,7 @@
         <v>308</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G14" t="s">
         <v>309</v>
@@ -9921,7 +9920,7 @@
         <v>50089</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>303</v>
@@ -9950,7 +9949,7 @@
         <v>319</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G18" t="s">
         <v>320</v>
@@ -9971,14 +9970,14 @@
         <v>50097</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D19" s="3"/>
       <c r="E19" s="2" t="s">
         <v>322</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H19" t="s">
         <v>285</v>
@@ -10000,7 +9999,7 @@
         <v>323</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="G20" t="s">
         <v>304</v>
@@ -10025,13 +10024,13 @@
         <v>324</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="G21" t="s">
         <v>325</v>
       </c>
       <c r="H21" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="I21" s="2"/>
       <c r="K21" s="2"/>
@@ -10044,13 +10043,13 @@
         <v>50100</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>326</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G22" t="s">
         <v>320</v>
@@ -10075,10 +10074,10 @@
       </c>
       <c r="D23" s="3"/>
       <c r="E23" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H23" t="s">
         <v>285</v>
@@ -10101,7 +10100,7 @@
         <v>328</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G24" t="s">
         <v>320</v>
@@ -10128,7 +10127,7 @@
         <v>330</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="G25" t="s">
         <v>304</v>
@@ -10153,7 +10152,7 @@
         <v>331</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="G26" t="s">
         <v>320</v>
@@ -10178,7 +10177,7 @@
         <v>332</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G27" t="s">
         <v>304</v>
@@ -10203,7 +10202,7 @@
         <v>333</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="G28" t="s">
         <v>304</v>
@@ -10227,7 +10226,9 @@
       <c r="E29" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="F29" s="2"/>
+      <c r="F29" s="2" t="s">
+        <v>448</v>
+      </c>
       <c r="G29" t="s">
         <v>335</v>
       </c>
@@ -10242,16 +10243,13 @@
         <v>31</v>
       </c>
       <c r="B30">
-        <v>50130</v>
-      </c>
-      <c r="C30">
-        <v>50126</v>
+        <v>50108</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="G30" t="s">
         <v>320</v>
@@ -10269,22 +10267,22 @@
         <v>32</v>
       </c>
       <c r="B31">
-        <v>50131</v>
+        <v>50109</v>
       </c>
       <c r="C31">
-        <v>50130</v>
+        <v>50108</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>337</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G31" t="s">
-        <v>338</v>
+        <v>6</v>
       </c>
       <c r="H31" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="I31" s="2"/>
       <c r="K31" s="2"/>
@@ -10294,22 +10292,22 @@
         <v>33</v>
       </c>
       <c r="B32">
-        <v>50132</v>
+        <v>50110</v>
       </c>
       <c r="C32">
-        <v>50131</v>
+        <v>50109</v>
       </c>
       <c r="E32" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="F32" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="F32" s="2" t="s">
-        <v>382</v>
-      </c>
       <c r="G32" t="s">
-        <v>338</v>
+        <v>6</v>
       </c>
       <c r="H32" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="I32" s="2"/>
       <c r="K32" s="2"/>
@@ -10319,22 +10317,22 @@
         <v>34</v>
       </c>
       <c r="B33">
-        <v>50133</v>
+        <v>50111</v>
       </c>
       <c r="C33">
-        <v>50132</v>
+        <v>50110</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F33" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="G33" t="s">
+        <v>6</v>
+      </c>
+      <c r="H33" t="s">
         <v>387</v>
-      </c>
-      <c r="G33" t="s">
-        <v>338</v>
-      </c>
-      <c r="H33" t="s">
-        <v>388</v>
       </c>
       <c r="I33" s="2"/>
       <c r="K33" s="2"/>
@@ -10403,16 +10401,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>50108</v>
+        <v>50112</v>
       </c>
       <c r="C2">
         <v>50105</v>
       </c>
       <c r="E2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="F2" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="G2" t="s">
         <v>6</v>
@@ -10427,19 +10425,19 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>50109</v>
+        <v>50113</v>
       </c>
       <c r="C3">
-        <v>50108</v>
+        <v>50112</v>
       </c>
       <c r="E3" t="s">
+        <v>430</v>
+      </c>
+      <c r="F3" t="s">
         <v>431</v>
       </c>
-      <c r="F3" t="s">
-        <v>432</v>
-      </c>
       <c r="G3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H3" t="s">
         <v>124</v>
@@ -10451,19 +10449,19 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>50110</v>
+        <v>50114</v>
       </c>
       <c r="C4">
-        <v>50109</v>
+        <v>50113</v>
       </c>
       <c r="E4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F4" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="G4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H4" t="s">
         <v>124</v>
@@ -10475,19 +10473,19 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>50111</v>
+        <v>50115</v>
       </c>
       <c r="C5">
-        <v>50110</v>
+        <v>50114</v>
       </c>
       <c r="E5" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="F5" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="G5" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H5" t="s">
         <v>124</v>
@@ -10499,19 +10497,19 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>50112</v>
+        <v>50116</v>
       </c>
       <c r="C6">
-        <v>50111</v>
+        <v>50115</v>
       </c>
       <c r="E6" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="F6" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="G6" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H6" t="s">
         <v>124</v>
@@ -10523,19 +10521,19 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>50113</v>
+        <v>50117</v>
       </c>
       <c r="C7">
-        <v>50112</v>
+        <v>50116</v>
       </c>
       <c r="E7" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="F7" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="G7" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H7" t="s">
         <v>124</v>
@@ -10547,19 +10545,19 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>50114</v>
+        <v>50118</v>
       </c>
       <c r="C8">
-        <v>50113</v>
+        <v>50117</v>
       </c>
       <c r="E8" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="F8" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="G8" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H8" t="s">
         <v>124</v>
@@ -10571,19 +10569,19 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>50115</v>
+        <v>50119</v>
       </c>
       <c r="C9">
-        <v>50114</v>
+        <v>50118</v>
       </c>
       <c r="E9" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="F9" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G9" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H9" t="s">
         <v>124</v>
@@ -10595,16 +10593,16 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>50116</v>
+        <v>50120</v>
       </c>
       <c r="C10">
-        <v>50115</v>
+        <v>50119</v>
       </c>
       <c r="E10" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="F10" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="G10" t="s">
         <v>6</v>
@@ -10619,19 +10617,19 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>50117</v>
+        <v>50121</v>
       </c>
       <c r="C11">
-        <v>50116</v>
+        <v>50120</v>
       </c>
       <c r="E11" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="F11" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G11" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="I11" s="2"/>
     </row>
@@ -10640,19 +10638,19 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>50118</v>
+        <v>50122</v>
       </c>
       <c r="C12">
-        <v>50117</v>
+        <v>50121</v>
       </c>
       <c r="E12" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="F12" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G12" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="I12" s="2"/>
     </row>
@@ -10661,19 +10659,19 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>50119</v>
+        <v>50123</v>
       </c>
       <c r="C13">
-        <v>50118</v>
+        <v>50122</v>
       </c>
       <c r="E13" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="F13" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="G13" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="I13" s="2"/>
     </row>
@@ -10682,22 +10680,22 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>50120</v>
+        <v>50124</v>
       </c>
       <c r="C14">
-        <v>50119</v>
+        <v>50123</v>
       </c>
       <c r="E14" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="F14" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="G14" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -10705,19 +10703,19 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>50121</v>
+        <v>50125</v>
       </c>
       <c r="C15">
-        <v>50120</v>
+        <v>50124</v>
       </c>
       <c r="E15" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="F15" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="G15" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="I15" s="2"/>
     </row>
@@ -10726,19 +10724,19 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>50122</v>
+        <v>50126</v>
       </c>
       <c r="C16">
-        <v>50121</v>
+        <v>50125</v>
       </c>
       <c r="E16" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="F16" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="G16" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="I16" s="2"/>
     </row>
@@ -10747,19 +10745,19 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>50123</v>
+        <v>50127</v>
       </c>
       <c r="C17">
-        <v>50122</v>
+        <v>50126</v>
       </c>
       <c r="E17" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="F17" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G17" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="I17" s="2"/>
     </row>
@@ -10768,19 +10766,19 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>50124</v>
+        <v>50128</v>
       </c>
       <c r="C18">
-        <v>50123</v>
+        <v>50127</v>
       </c>
       <c r="E18" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="F18" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G18" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="I18" s="2"/>
     </row>
@@ -10789,16 +10787,19 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>50125</v>
+        <v>50129</v>
       </c>
       <c r="C19">
-        <v>50124</v>
+        <v>50128</v>
       </c>
       <c r="E19" t="s">
-        <v>403</v>
+        <v>402</v>
+      </c>
+      <c r="F19" t="s">
+        <v>448</v>
       </c>
       <c r="G19" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="I19" s="2"/>
     </row>
@@ -10807,19 +10808,19 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>50126</v>
+        <v>50130</v>
       </c>
       <c r="C20">
-        <v>50124</v>
+        <v>50128</v>
       </c>
       <c r="E20" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="F20" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G20" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="I20" s="2"/>
     </row>
@@ -10828,19 +10829,19 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>50127</v>
+        <v>50131</v>
       </c>
       <c r="C21">
-        <v>50122</v>
+        <v>50130</v>
       </c>
       <c r="E21" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="F21" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="G21" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="I21" s="2"/>
     </row>
@@ -10849,19 +10850,19 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>50128</v>
+        <v>50132</v>
       </c>
       <c r="C22">
-        <v>50127</v>
+        <v>50130</v>
       </c>
       <c r="E22" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F22" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="G22" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="I22" s="2"/>
     </row>
@@ -10870,22 +10871,22 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>50129</v>
+        <v>50133</v>
       </c>
       <c r="C23">
-        <v>50128</v>
+        <v>50130</v>
       </c>
       <c r="E23" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="F23" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="G23" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -10893,16 +10894,16 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>50130</v>
+        <v>50134</v>
       </c>
       <c r="C24">
-        <v>50122</v>
+        <v>50128</v>
       </c>
       <c r="E24" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="F24" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="I24" s="2"/>
     </row>
@@ -10911,16 +10912,16 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>50131</v>
+        <v>50135</v>
       </c>
       <c r="C25">
-        <v>50130</v>
+        <v>50134</v>
       </c>
       <c r="E25" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="F25" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="I25" s="2"/>
     </row>
@@ -10929,16 +10930,16 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>50132</v>
+        <v>50136</v>
       </c>
       <c r="C26">
-        <v>50131</v>
+        <v>50135</v>
       </c>
       <c r="E26" t="s">
+        <v>445</v>
+      </c>
+      <c r="F26" t="s">
         <v>446</v>
-      </c>
-      <c r="F26" t="s">
-        <v>447</v>
       </c>
       <c r="I26" s="2"/>
     </row>
@@ -11439,13 +11440,13 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>351</v>
+      </c>
+      <c r="B1" t="s">
         <v>352</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>353</v>
-      </c>
-      <c r="C1" t="s">
-        <v>354</v>
       </c>
       <c r="E1" t="s">
         <v>0</v>
@@ -11457,13 +11458,13 @@
         <v>2</v>
       </c>
       <c r="H1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="I1" t="s">
         <v>281</v>
       </c>
       <c r="J1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="K1" t="s">
         <v>3</v>
@@ -11477,10 +11478,10 @@
         <v>59000</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>357</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>358</v>
       </c>
       <c r="G2" t="s">
         <v>20</v>
@@ -11489,7 +11490,7 @@
         <v>99</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -11500,16 +11501,16 @@
         <v>59001</v>
       </c>
       <c r="E3" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>360</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>361</v>
       </c>
       <c r="G3" t="s">
         <v>6</v>
       </c>
       <c r="H3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="I3" s="2"/>
     </row>
@@ -11524,19 +11525,19 @@
         <v>59001</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>362</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>363</v>
       </c>
       <c r="G4" t="s">
         <v>20</v>
       </c>
       <c r="H4" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -11550,16 +11551,16 @@
         <v>59002</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>365</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>366</v>
       </c>
       <c r="G5" t="s">
         <v>200</v>
       </c>
       <c r="H5" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="I5" s="2"/>
     </row>
@@ -11574,19 +11575,19 @@
         <v>59003</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="G6" t="s">
         <v>20</v>
       </c>
       <c r="H6" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
   </sheetData>

--- a/01_기획/02. 컨텐츠/컨텐츠_맵 설정.xlsx
+++ b/01_기획/02. 컨텐츠/컨텐츠_맵 설정.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="14385" yWindow="-15" windowWidth="14430" windowHeight="12060" tabRatio="687" firstSheet="1" activeTab="5"/>
+    <workbookView xWindow="14385" yWindow="-15" windowWidth="14430" windowHeight="12060" tabRatio="687" firstSheet="1" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="튜토리얼" sheetId="5" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="812" uniqueCount="449">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="820" uniqueCount="455">
   <si>
     <t>제목</t>
   </si>
@@ -924,9 +924,6 @@
     <t>C</t>
   </si>
   <si>
-    <t>오.. 동쪽 숲을 지나 오다니 대단한걸? 묵을 곳은 정했어? 딱히 정한 곳이 없다면 광산마을 여관으로 가봐. 음식은 별로지만 거기 주인인 줄리아는 최고야.</t>
-  </si>
-  <si>
     <t>작클레에게 한번 가 보라고 한다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -934,18 +931,12 @@
     <t>고고학자</t>
   </si>
   <si>
-    <t>고고학자? 글쎄... 고고학자는 모르겠고 작클레씨가 우리 마을에서 제일 똑똑하지. 궁금한게 있으면 마법 연구소에 한번 들려봐</t>
-  </si>
-  <si>
     <t>마법사 작클레</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>QuestTalk</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>리바이의 서가 있을 경우 :  난 작클레라고 하네. 네게 뭔가 볼 일이라도? 오.. 이것은!!!! 이걸 해석하려면 꽤 오래 걸리겠군. 뭔가를 알아내면 알려 주겠네. 리바이의 서가 없을 경우 : 난 작클레라고 하네. 네게 뭔가 볼 일이라도? 딱히 일이 없으면 방해하지 말게.</t>
   </si>
   <si>
     <t>리바이의 서가 있을 경우 : 뭔가를 알아내면 알려 주겠다고 한다.
@@ -956,9 +947,6 @@
     <t>리바이의 서의 비밀 1</t>
   </si>
   <si>
-    <t>오.. 왔는가? 모두 다 해석한 건 아니지만 이 책은 문을 여는 열쇠인 것 같네. 더 자세한 건 내 능력으론 힘들 것 같군. 아, 최근에 황무지에서 뭔가를 발견했다고 하더군. 일단 광물 조합장 코퍼씨를 만나 보게. </t>
-  </si>
-  <si>
     <t>자신이 해독하기엔 어려우니 황무지의 누구를 찾아가 보라고 한다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -971,15 +959,9 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>어서 오세요. 광산 마을을 처음인가요? 예전만 못하지만 그래도 광산 마을은 풍요로운 곳이랍니다. 뭐 필요한 게 있으면 말씀해 주세요.</t>
-  </si>
-  <si>
     <t>작클레의 호출</t>
   </si>
   <si>
-    <t>여기 계셨군요. 아까 작클레씨가 찾던데 만나 보셨나요? 지금 바로 마법 연구소로 가 보세요.</t>
-  </si>
-  <si>
     <t>다음 지역으로 이동해 보세요</t>
   </si>
   <si>
@@ -1008,9 +990,6 @@
     <t>QuestTalk</t>
   </si>
   <si>
-    <t>골드 주머니가 있는 경우 : 엉엉 ㅠㅠ 누가 우리집에 들어가 내 전 재산을 훔쳐갔어. 뭐, 그게 너라구? 뭐 돈을 돌려 준다니 다행이긴 하지만 도둑질은 나쁜거야. 우리 밭에서 호박을 수확해 준다면 용서해 줄께. 골드가 없는 경우 : 저러다 호박이 다 썩어 버리겠어. 바쁘니까 저리 좀 비켜줄래?</t>
-  </si>
-  <si>
     <t>누군가 자신의 집에서 돈을 훔쳐가서 빈털터리가 되었다고 한다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1035,9 +1014,6 @@
   <si>
     <t>GiveItem</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>호박이 있을 경우 : 고마워. 덕분에 걱정을 덜었어. 호박이 없을 경우 : 뭐야? 아직도 안 간거야? 빨리 빨리 하라구.</t>
   </si>
   <si>
     <t>광물 조합장 코퍼</t>
@@ -1536,6 +1512,62 @@
   </si>
   <si>
     <t xml:space="preserve">보물 위에 가만히 서 있으면 보상을 받을 수 있습니다. </t>
+  </si>
+  <si>
+    <t>오.. 동쪽 숲을 지나 오다니 대단한걸? 묵을 곳은 정했어? 딱히 정한 곳이 없다면 광산마을 여관으로 가봐. 음식은 별로지만 거기 주인인 줄리아는 최고야.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고고학자? 글쎄... 고고학자는 모르겠고 작클레씨가 우리 마을에서 제일 똑똑하지. 궁금한게 있으면 마법 연구소에 한번 들려봐.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>리바이의 서가 있을 경우 :  난 작클레라고 하네. 네게 뭔가 볼 일이라도? 오.. 이것은!!!! 이걸 해석하려면 꽤 오래 걸리겠군. 뭔가를 알아내면 알려 주겠네. 리바이의 서가 없을 경우 : 난 작클레라고 하네. 네게 뭔가 볼 일이라도? 딱히 일이 없으면 방해하지 말게.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>어서 오세요. 광산 마을을 처음인가요? 예전만 못하지만 그래도 광산 마을은 풍요로운 곳이랍니다. 뭐 필요한 게 있으면 말씀해 주세요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>여기 계셨군요. 아까 작클레씨가 찾던데 만나 보셨나요? 지금 바로 마법 연구소로 가 보세요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오.. 왔는가? 모두 다 해석한 건 아니지만 이 책은 문을 여는 열쇠인 것 같네. 더 자세한 건 내 능력으론 힘들 것 같군. 아, 최근에 황무지에서 뭔가를 발견했다고 하더군. 일단 광물 조합장 코퍼씨를 만나 보게. </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>골드 주머니가 있는 경우 : 엉엉 ㅠㅠ 누가 우리집에 들어가 내 전 재산을 훔쳐갔어. 뭐, 그게 너라구? 뭐 돈을 돌려 준다니 다행이긴 하지만 도둑질은 나쁜거야. 우리 밭에서 호박을 수확해 준다면 용서해 줄께. 골드가 없는 경우 : 저러다 호박이 다 썩어 버리겠어. 바쁘니까 저리 좀 비켜줄래?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>호박이 있을 경우 : 고마워. 덕분에 걱정을 덜었어. 호박이 없을 경우 : 뭐야? 아직도 안 간거야? 빨리 빨리 하라구.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>묘지에 망령이 돌아다닌다고 하니 걱정이군. 혹시…? 아닐세, 자네 실력으론 무리일꺼야. 뭐 굳이 하겠다면야… 잘 부탁하네.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>리바이의 서가 있을 경우 : 뭘 잘 못 듣고 왔나 보군. 뭐? 아 작클레씨가 알려 줬다구? 하여간… 황무지에서 유적을 발견했는데, 그게 관계가 있을지도 모른다더군. 자세한 건 탐사대가 돌아와 봐야 알 수 있겠지. 리바이의 서가 없을 경우: 내게 무슨 볼 일이라도 있는 건가? 바쁘니까 비켜 주게나.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이런 들켜 버렸군. 메데이아님께 영광을!!! 윽!!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아이템이 있는 경우: 벌써 처치한 것인가? 정말 대단한 실력이군. 고맙네. 아이템이 없는 경우 : 역시 자네에겐 무리였군. 너무 애쓰진 말게.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>벌써 메데이아 귀에 들어간건가? 그렇게 비밀유지에 노력했건만… 이렇게 된 이상 서둘러야겠군. 자네는 어서 황무지에 있는 탐사대에게 이 사실을 전해 주게.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>안녕하세요. 황무지로 가신다구요? 황무지는 위험한 곳이니 조심하세요. 도움이 될지는 모르겠지만, 저 위 창고에 여비에 보탬이 되게 준비해 두었습니다. 가기 전에 들려 보세요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -9521,7 +9553,7 @@
         <v>283</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="G2" t="s">
         <v>284</v>
@@ -9530,10 +9562,10 @@
         <v>285</v>
       </c>
       <c r="I2" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="K2" s="2" t="s">
         <v>286</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="57.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -9548,10 +9580,10 @@
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="G3" t="s">
         <v>20</v>
@@ -9560,7 +9592,7 @@
         <v>285</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>289</v>
+        <v>442</v>
       </c>
       <c r="K3" s="2"/>
     </row>
@@ -9575,10 +9607,10 @@
         <v>50081</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="G4" t="s">
         <v>6</v>
@@ -9600,22 +9632,22 @@
         <v>50082</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="G5" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="H5" t="s">
         <v>285</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>292</v>
+        <v>443</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -9629,10 +9661,10 @@
         <v>50080</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="G6" t="s">
         <v>6</v>
@@ -9654,10 +9686,10 @@
         <v>50084</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="G7" t="s">
         <v>284</v>
@@ -9666,7 +9698,7 @@
         <v>285</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>299</v>
+        <v>444</v>
       </c>
       <c r="K7" s="2"/>
     </row>
@@ -9678,13 +9710,13 @@
         <v>50086</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="G8" t="s">
         <v>20</v>
@@ -9693,7 +9725,7 @@
         <v>285</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>301</v>
+        <v>445</v>
       </c>
       <c r="K8" s="2"/>
     </row>
@@ -9708,10 +9740,10 @@
         <v>50086</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="G9" t="s">
         <v>6</v>
@@ -9733,10 +9765,10 @@
         <v>50087</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="G10" t="s">
         <v>284</v>
@@ -9745,10 +9777,10 @@
         <v>285</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>295</v>
+        <v>446</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -9762,10 +9794,10 @@
         <v>50085</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="G11" t="s">
         <v>6</v>
@@ -9787,13 +9819,13 @@
         <v>50085</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="G12" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="H12" t="s">
         <v>285</v>
@@ -9812,13 +9844,13 @@
         <v>50090</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="G13" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="H13" t="s">
         <v>285</v>
@@ -9837,22 +9869,22 @@
         <v>50091</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="G14" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="H14" t="s">
         <v>285</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>310</v>
+        <v>447</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -9866,19 +9898,19 @@
         <v>50092</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="G15" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="H15" t="s">
         <v>285</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="K15" s="2"/>
     </row>
@@ -9893,19 +9925,19 @@
         <v>50093</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="G16" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="H16" t="s">
         <v>285</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>318</v>
+        <v>448</v>
       </c>
       <c r="K16" s="2"/>
     </row>
@@ -9920,13 +9952,13 @@
         <v>50089</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="G17" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="H17" t="s">
         <v>285</v>
@@ -9946,20 +9978,22 @@
       </c>
       <c r="D18" s="3"/>
       <c r="E18" s="2" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="G18" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="H18" t="s">
         <v>285</v>
       </c>
-      <c r="I18" s="2"/>
+      <c r="I18" s="2" t="s">
+        <v>449</v>
+      </c>
       <c r="K18" s="2" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="57.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -9970,19 +10004,24 @@
         <v>50097</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="D19" s="3"/>
       <c r="E19" s="2" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>371</v>
+        <v>363</v>
+      </c>
+      <c r="G19" t="s">
+        <v>303</v>
       </c>
       <c r="H19" t="s">
         <v>285</v>
       </c>
-      <c r="I19" s="2"/>
+      <c r="I19" s="2" t="s">
+        <v>450</v>
+      </c>
       <c r="K19" s="2"/>
     </row>
     <row r="20" spans="1:11" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -9996,13 +10035,13 @@
         <v>50096</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>439</v>
+        <v>431</v>
       </c>
       <c r="G20" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="H20" t="s">
         <v>285</v>
@@ -10021,16 +10060,16 @@
         <v>50098</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="G21" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="H21" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="I21" s="2"/>
       <c r="K21" s="2"/>
@@ -10043,23 +10082,25 @@
         <v>50100</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="G22" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="H22" t="s">
         <v>285</v>
       </c>
-      <c r="I22" s="2"/>
+      <c r="I22" s="2" t="s">
+        <v>451</v>
+      </c>
       <c r="K22" s="2" t="s">
-        <v>327</v>
+        <v>319</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="58.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -10074,15 +10115,20 @@
       </c>
       <c r="D23" s="3"/>
       <c r="E23" s="2" t="s">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>350</v>
+        <v>342</v>
+      </c>
+      <c r="G23" t="s">
+        <v>303</v>
       </c>
       <c r="H23" t="s">
         <v>285</v>
       </c>
-      <c r="I23" s="2"/>
+      <c r="I23" s="2" t="s">
+        <v>452</v>
+      </c>
       <c r="K23" s="2"/>
     </row>
     <row r="24" spans="1:11" ht="58.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -10097,20 +10143,22 @@
       </c>
       <c r="D24" s="3"/>
       <c r="E24" s="2" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="G24" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="H24" t="s">
         <v>285</v>
       </c>
-      <c r="I24" s="2"/>
+      <c r="I24" s="2" t="s">
+        <v>453</v>
+      </c>
       <c r="K24" s="2" t="s">
-        <v>329</v>
+        <v>321</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -10124,13 +10172,13 @@
         <v>50101</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="G25" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="H25" t="s">
         <v>285</v>
@@ -10149,18 +10197,20 @@
         <v>50103</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="G26" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="H26" t="s">
         <v>285</v>
       </c>
-      <c r="I26" s="2"/>
+      <c r="I26" s="2" t="s">
+        <v>454</v>
+      </c>
       <c r="K26" s="2"/>
     </row>
     <row r="27" spans="1:11" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -10174,13 +10224,13 @@
         <v>50104</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="G27" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="H27" t="s">
         <v>285</v>
@@ -10199,13 +10249,13 @@
         <v>50104</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="G28" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="H28" t="s">
         <v>285</v>
@@ -10224,13 +10274,13 @@
         <v>50106</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>448</v>
+        <v>440</v>
       </c>
       <c r="G29" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="H29" t="s">
         <v>285</v>
@@ -10246,20 +10296,20 @@
         <v>50108</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="G30" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="H30" t="s">
         <v>124</v>
       </c>
       <c r="I30" s="2"/>
       <c r="K30" s="2" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -10273,16 +10323,16 @@
         <v>50108</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="G31" t="s">
         <v>6</v>
       </c>
       <c r="H31" t="s">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="I31" s="2"/>
       <c r="K31" s="2"/>
@@ -10298,16 +10348,16 @@
         <v>50109</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="G32" t="s">
         <v>6</v>
       </c>
       <c r="H32" t="s">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="I32" s="2"/>
       <c r="K32" s="2"/>
@@ -10323,16 +10373,16 @@
         <v>50110</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="G33" t="s">
         <v>6</v>
       </c>
       <c r="H33" t="s">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="I33" s="2"/>
       <c r="K33" s="2"/>
@@ -10407,10 +10457,10 @@
         <v>50105</v>
       </c>
       <c r="E2" t="s">
-        <v>388</v>
+        <v>380</v>
       </c>
       <c r="F2" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="G2" t="s">
         <v>6</v>
@@ -10431,13 +10481,13 @@
         <v>50112</v>
       </c>
       <c r="E3" t="s">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="F3" t="s">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="G3" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="H3" t="s">
         <v>124</v>
@@ -10455,13 +10505,13 @@
         <v>50113</v>
       </c>
       <c r="E4" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="F4" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="G4" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="H4" t="s">
         <v>124</v>
@@ -10479,13 +10529,13 @@
         <v>50114</v>
       </c>
       <c r="E5" t="s">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="F5" t="s">
-        <v>432</v>
+        <v>424</v>
       </c>
       <c r="G5" t="s">
-        <v>420</v>
+        <v>412</v>
       </c>
       <c r="H5" t="s">
         <v>124</v>
@@ -10503,13 +10553,13 @@
         <v>50115</v>
       </c>
       <c r="E6" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="F6" t="s">
-        <v>433</v>
+        <v>425</v>
       </c>
       <c r="G6" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="H6" t="s">
         <v>124</v>
@@ -10527,13 +10577,13 @@
         <v>50116</v>
       </c>
       <c r="E7" t="s">
-        <v>391</v>
+        <v>383</v>
       </c>
       <c r="F7" t="s">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="G7" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="H7" t="s">
         <v>124</v>
@@ -10551,13 +10601,13 @@
         <v>50117</v>
       </c>
       <c r="E8" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="F8" t="s">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="G8" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="H8" t="s">
         <v>124</v>
@@ -10575,13 +10625,13 @@
         <v>50118</v>
       </c>
       <c r="E9" t="s">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="F9" t="s">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="G9" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="H9" t="s">
         <v>124</v>
@@ -10599,10 +10649,10 @@
         <v>50119</v>
       </c>
       <c r="E10" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="F10" t="s">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="G10" t="s">
         <v>6</v>
@@ -10623,13 +10673,13 @@
         <v>50120</v>
       </c>
       <c r="E11" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="F11" t="s">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="G11" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="I11" s="2"/>
     </row>
@@ -10644,13 +10694,13 @@
         <v>50121</v>
       </c>
       <c r="E12" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="F12" t="s">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="G12" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="I12" s="2"/>
     </row>
@@ -10665,13 +10715,13 @@
         <v>50122</v>
       </c>
       <c r="E13" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="F13" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="G13" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="I13" s="2"/>
     </row>
@@ -10686,16 +10736,16 @@
         <v>50123</v>
       </c>
       <c r="E14" t="s">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="F14" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="G14" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>442</v>
+        <v>434</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -10709,13 +10759,13 @@
         <v>50124</v>
       </c>
       <c r="E15" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="F15" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="G15" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="I15" s="2"/>
     </row>
@@ -10730,13 +10780,13 @@
         <v>50125</v>
       </c>
       <c r="E16" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="F16" t="s">
-        <v>436</v>
+        <v>428</v>
       </c>
       <c r="G16" t="s">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="I16" s="2"/>
     </row>
@@ -10751,13 +10801,13 @@
         <v>50126</v>
       </c>
       <c r="E17" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="F17" t="s">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="G17" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="I17" s="2"/>
     </row>
@@ -10772,13 +10822,13 @@
         <v>50127</v>
       </c>
       <c r="E18" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="F18" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="G18" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="I18" s="2"/>
     </row>
@@ -10793,13 +10843,13 @@
         <v>50128</v>
       </c>
       <c r="E19" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="F19" t="s">
-        <v>448</v>
+        <v>440</v>
       </c>
       <c r="G19" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="I19" s="2"/>
     </row>
@@ -10814,13 +10864,13 @@
         <v>50128</v>
       </c>
       <c r="E20" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="F20" t="s">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="G20" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="I20" s="2"/>
     </row>
@@ -10835,13 +10885,13 @@
         <v>50130</v>
       </c>
       <c r="E21" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="F21" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="G21" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="I21" s="2"/>
     </row>
@@ -10856,13 +10906,13 @@
         <v>50130</v>
       </c>
       <c r="E22" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="F22" t="s">
+        <v>409</v>
+      </c>
+      <c r="G22" t="s">
         <v>417</v>
-      </c>
-      <c r="G22" t="s">
-        <v>425</v>
       </c>
       <c r="I22" s="2"/>
     </row>
@@ -10877,16 +10927,16 @@
         <v>50130</v>
       </c>
       <c r="E23" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="F23" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="G23" t="s">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>443</v>
+        <v>435</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -10900,10 +10950,10 @@
         <v>50128</v>
       </c>
       <c r="E24" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="F24" t="s">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="I24" s="2"/>
     </row>
@@ -10918,10 +10968,10 @@
         <v>50134</v>
       </c>
       <c r="E25" t="s">
-        <v>444</v>
+        <v>436</v>
       </c>
       <c r="F25" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="I25" s="2"/>
     </row>
@@ -10936,10 +10986,10 @@
         <v>50135</v>
       </c>
       <c r="E26" t="s">
-        <v>445</v>
+        <v>437</v>
       </c>
       <c r="F26" t="s">
-        <v>446</v>
+        <v>438</v>
       </c>
       <c r="I26" s="2"/>
     </row>
@@ -11440,13 +11490,13 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="B1" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="C1" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="E1" t="s">
         <v>0</v>
@@ -11458,13 +11508,13 @@
         <v>2</v>
       </c>
       <c r="H1" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="I1" t="s">
         <v>281</v>
       </c>
       <c r="J1" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="K1" t="s">
         <v>3</v>
@@ -11478,10 +11528,10 @@
         <v>59000</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="G2" t="s">
         <v>20</v>
@@ -11490,7 +11540,7 @@
         <v>99</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -11501,16 +11551,16 @@
         <v>59001</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="G3" t="s">
         <v>6</v>
       </c>
       <c r="H3" t="s">
-        <v>447</v>
+        <v>439</v>
       </c>
       <c r="I3" s="2"/>
     </row>
@@ -11525,19 +11575,19 @@
         <v>59001</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="G4" t="s">
         <v>20</v>
       </c>
       <c r="H4" t="s">
-        <v>447</v>
+        <v>439</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -11551,16 +11601,16 @@
         <v>59002</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="G5" t="s">
         <v>200</v>
       </c>
       <c r="H5" t="s">
-        <v>447</v>
+        <v>439</v>
       </c>
       <c r="I5" s="2"/>
     </row>
@@ -11575,19 +11625,19 @@
         <v>59003</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="G6" t="s">
         <v>20</v>
       </c>
       <c r="H6" t="s">
-        <v>447</v>
+        <v>439</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
     </row>
   </sheetData>
